--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4F6B12-BD27-4E9D-8A83-7CF4B86196E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78EA88C-3D1A-4718-85C2-42C3A362F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="FB" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="15">
   <si>
     <t>Day</t>
   </si>
@@ -63,15 +64,6 @@
     <t>CHD-Buyer-Acquisition-6April</t>
   </si>
   <si>
-    <t>Reporting starts</t>
-  </si>
-  <si>
-    <t>Campaign name</t>
-  </si>
-  <si>
-    <t>Amount spent (INR)</t>
-  </si>
-  <si>
     <t>Chandigarh-UCR-Catalogue-Ads</t>
   </si>
   <si>
@@ -79,6 +71,24 @@
   </si>
   <si>
     <t>Nasik-Search-Buy-UsedCar-8april</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Campaign Name</t>
+  </si>
+  <si>
+    <t>Amount Spent</t>
+  </si>
+  <si>
+    <t>Nashik-pmax-Used-car-16june</t>
+  </si>
+  <si>
+    <t>UC-DSA-Nashik-UsedCars</t>
+  </si>
+  <si>
+    <t>Nashik-DSA-UsedCars-Discovery</t>
   </si>
 </sst>
 </file>
@@ -452,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C221"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -472,2268 +482,2268 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46113</v>
+        <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>79.209999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46114</v>
+        <v>46186</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>521.09</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46115</v>
+        <v>46187</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1197.73</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46116</v>
+        <v>46188</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>778.85</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46117</v>
+        <v>46189</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>617.65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46118</v>
+        <v>46183</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>298.89</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>64.97</v>
+        <v>628.70000000000005</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>628.70000000000005</v>
+        <v>632.29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>632.29</v>
+        <v>374.88</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>374.88</v>
+        <v>532.29999999999995</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>532.29999999999995</v>
+        <v>620.17999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>620.17999999999995</v>
+        <v>1437.37</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>1437.37</v>
+        <v>1094.69</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>1094.69</v>
+        <v>911.37</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>911.37</v>
+        <v>1061.49</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>1061.49</v>
+        <v>1085.51</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>1085.51</v>
+        <v>999.47</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>999.47</v>
+        <v>975.32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>975.32</v>
+        <v>1047.22</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>1047.22</v>
+        <v>1259.8699999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>1259.8699999999999</v>
+        <v>1064.55</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>1064.55</v>
+        <v>996.48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>996.48</v>
+        <v>1312.03</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>1312.03</v>
+        <v>1028.4100000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>1028.4100000000001</v>
+        <v>788.39</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>788.39</v>
+        <v>773.31</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>773.31</v>
+        <v>773.36</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>773.36</v>
+        <v>776.21</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>776.21</v>
+        <v>896.44</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>896.44</v>
+        <v>977.68</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>977.68</v>
+        <v>1365.79</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>1365.79</v>
+        <v>883.13</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>883.13</v>
+        <v>885.01</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C36">
-        <v>885.01</v>
+        <v>771.48</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>771.48</v>
+        <v>1129.58</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>1129.58</v>
+        <v>1237.75</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>1237.75</v>
+        <v>1036.03</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>1036.03</v>
+        <v>1041.58</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>1041.58</v>
+        <v>1050.2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C42">
-        <v>1050.2</v>
+        <v>963.55</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C43">
-        <v>963.55</v>
+        <v>852.6</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>852.6</v>
+        <v>929.18</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C45">
-        <v>929.18</v>
+        <v>1007.08</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>1007.08</v>
+        <v>1190.55</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C47">
-        <v>1190.55</v>
+        <v>1025.94</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C48">
-        <v>1025.94</v>
+        <v>883.7</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C49">
-        <v>883.7</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50">
-        <v>822.74</v>
+        <v>889.78</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51">
-        <v>889.78</v>
+        <v>1238.71</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52">
-        <v>1238.71</v>
+        <v>960.3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C53">
-        <v>960.3</v>
+        <v>1035.1300000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C54">
-        <v>1035.1300000000001</v>
+        <v>935.29</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C55">
-        <v>935.29</v>
+        <v>1300.27</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C56">
-        <v>1300.27</v>
+        <v>1691.22</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C57">
-        <v>1691.22</v>
+        <v>1719.87</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C58">
-        <v>1719.87</v>
+        <v>1581.56</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C59">
-        <v>1581.56</v>
+        <v>1577.46</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C60">
-        <v>1577.46</v>
+        <v>1602.4</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C61">
-        <v>1602.4</v>
+        <v>1425.5</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C62">
-        <v>1425.5</v>
+        <v>853.4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C63">
-        <v>853.4</v>
+        <v>576.04</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>3125.43</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C65">
-        <v>576.04</v>
+        <v>2189.2600000000002</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46113</v>
+        <v>46179</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1761.01</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46114</v>
+        <v>46180</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1829.97</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46115</v>
+        <v>46181</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2359.3000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46116</v>
+        <v>46182</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2694.6</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46117</v>
+        <v>46183</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46118</v>
+        <v>46184</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1690.68</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46119</v>
+        <v>46185</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>911.1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46120</v>
+        <v>46186</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C73">
-        <v>31.83</v>
+        <v>803.62</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46121</v>
+        <v>46187</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C74">
-        <v>1029.69</v>
+        <v>656.27</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46122</v>
+        <v>46188</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C75">
-        <v>663.55</v>
+        <v>679.73</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46123</v>
+        <v>46189</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C76">
-        <v>373.1</v>
+        <v>879.71</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46124</v>
+        <v>46120</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>595.20000000000005</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>625.48</v>
+        <v>1029.69</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
-        <v>1455.55</v>
+        <v>663.55</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46127</v>
+        <v>46123</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
-        <v>980.89</v>
+        <v>373.1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46128</v>
+        <v>46124</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81">
-        <v>1020.87</v>
+        <v>595.20000000000005</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46129</v>
+        <v>46125</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
       <c r="C82">
-        <v>1074.21</v>
+        <v>625.48</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>1063.98</v>
+        <v>1455.55</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46131</v>
+        <v>46127</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>1040.55</v>
+        <v>980.89</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>992.2</v>
+        <v>1020.87</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>962.16</v>
+        <v>1074.21</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46134</v>
+        <v>46130</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>1249.56</v>
+        <v>1063.98</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46135</v>
+        <v>46131</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>1047.03</v>
+        <v>1040.55</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46136</v>
+        <v>46132</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>1220.19</v>
+        <v>992.2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46137</v>
+        <v>46133</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
       <c r="C90">
-        <v>1267.83</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46138</v>
+        <v>46134</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>1000.43</v>
+        <v>1249.56</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
-        <v>750.37</v>
+        <v>1047.03</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
       <c r="C93">
-        <v>750.11</v>
+        <v>1220.19</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46141</v>
+        <v>46137</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94">
-        <v>749.15</v>
+        <v>1267.83</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46142</v>
+        <v>46138</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>750.4</v>
+        <v>1000.43</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96">
-        <v>733.27</v>
+        <v>750.37</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46144</v>
+        <v>46140</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97">
-        <v>1008.56</v>
+        <v>750.11</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46145</v>
+        <v>46141</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
       <c r="C98">
-        <v>1267.73</v>
+        <v>749.15</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99">
-        <v>1106.75</v>
+        <v>750.4</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
       <c r="C100">
-        <v>1012.99</v>
+        <v>733.27</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46148</v>
+        <v>46144</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
       <c r="C101">
-        <v>743.27</v>
+        <v>1008.56</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46149</v>
+        <v>46145</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
       <c r="C102">
-        <v>1104.6600000000001</v>
+        <v>1267.73</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
       <c r="C103">
-        <v>1062.3499999999999</v>
+        <v>1106.75</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46151</v>
+        <v>46147</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
       <c r="C104">
-        <v>1075.5</v>
+        <v>1012.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46152</v>
+        <v>46148</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105">
-        <v>924.44</v>
+        <v>743.27</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106">
-        <v>976.86</v>
+        <v>1104.6600000000001</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107">
-        <v>981.19</v>
+        <v>1062.3499999999999</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46155</v>
+        <v>46151</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108">
-        <v>1026.52</v>
+        <v>1075.5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46156</v>
+        <v>46152</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109">
-        <v>1107.58</v>
+        <v>924.44</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110">
-        <v>1097.79</v>
+        <v>976.86</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46158</v>
+        <v>46154</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
       <c r="C111">
-        <v>862.95</v>
+        <v>981.19</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46159</v>
+        <v>46155</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
       <c r="C112">
-        <v>1015.09</v>
+        <v>1026.52</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
       </c>
       <c r="C113">
-        <v>1062.22</v>
+        <v>1107.58</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
       <c r="C114">
-        <v>988.49</v>
+        <v>1097.79</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46162</v>
+        <v>46158</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
       <c r="C115">
-        <v>778.96</v>
+        <v>862.95</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46163</v>
+        <v>46159</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116">
-        <v>856.43</v>
+        <v>1015.09</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
       <c r="C117">
-        <v>1182.79</v>
+        <v>1062.22</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46165</v>
+        <v>46161</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
       <c r="C118">
-        <v>1057.1099999999999</v>
+        <v>988.49</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46166</v>
+        <v>46162</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119">
-        <v>966.22</v>
+        <v>778.96</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
       <c r="C120">
-        <v>934.12</v>
+        <v>856.43</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
       <c r="C121">
-        <v>890.5</v>
+        <v>1182.79</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46169</v>
+        <v>46165</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122">
-        <v>833.8</v>
+        <v>1057.1099999999999</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46170</v>
+        <v>46166</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
       <c r="C123">
-        <v>872.27</v>
+        <v>966.22</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
       <c r="C124">
-        <v>979.23</v>
+        <v>934.12</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46172</v>
+        <v>46168</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
       <c r="C125">
-        <v>960.49</v>
+        <v>890.5</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
       <c r="C126">
-        <v>930.07</v>
+        <v>833.8</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
       <c r="C127">
-        <v>897.07</v>
+        <v>872.27</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
       <c r="C128">
-        <v>1161.46</v>
+        <v>979.23</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46176</v>
+        <v>46172</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
       <c r="C129">
-        <v>1026.26</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46113</v>
+        <v>46173</v>
       </c>
       <c r="B130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>930.07</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46114</v>
+        <v>46174</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>897.07</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46115</v>
+        <v>46175</v>
       </c>
       <c r="B132" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1158.77</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46116</v>
+        <v>46176</v>
       </c>
       <c r="B133" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1026.26</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46117</v>
+        <v>46177</v>
       </c>
       <c r="B134" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>895.72</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46118</v>
+        <v>46178</v>
       </c>
       <c r="B135" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135">
-        <v>876.13</v>
+        <v>836.49</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46119</v>
+        <v>46179</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136">
-        <v>1522.15</v>
+        <v>1521.28</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46120</v>
+        <v>46180</v>
       </c>
       <c r="B137" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137">
-        <v>1482.18</v>
+        <v>1212.58</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46121</v>
+        <v>46181</v>
       </c>
       <c r="B138" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>997.89</v>
+        <v>981.26</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46122</v>
+        <v>46182</v>
       </c>
       <c r="B139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C139">
-        <v>1000.12</v>
+        <v>1002.08</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46123</v>
+        <v>46183</v>
       </c>
       <c r="B140" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>895.24</v>
+        <v>997.2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46124</v>
+        <v>46184</v>
       </c>
       <c r="B141" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>1014.46</v>
+        <v>822.2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46125</v>
+        <v>46185</v>
       </c>
       <c r="B142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
-        <v>772.98</v>
+        <v>669.78</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46126</v>
+        <v>46186</v>
       </c>
       <c r="B143" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>1057.8800000000001</v>
+        <v>1208.0999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46127</v>
+        <v>46187</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144">
-        <v>869.45</v>
+        <v>1582.98</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46128</v>
+        <v>46188</v>
       </c>
       <c r="B145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C145">
-        <v>845.41</v>
+        <v>931.83</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46129</v>
+        <v>46189</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146">
-        <v>863.08</v>
+        <v>920.5</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46130</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="s">
         <v>5</v>
       </c>
       <c r="C147">
-        <v>973.22</v>
+        <v>1482.18</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46131</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="s">
         <v>5</v>
       </c>
       <c r="C148">
-        <v>1320.17</v>
+        <v>997.89</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="s">
         <v>5</v>
       </c>
       <c r="C149">
-        <v>916.68</v>
+        <v>1000.12</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46133</v>
+        <v>46123</v>
       </c>
       <c r="B150" t="s">
         <v>5</v>
       </c>
       <c r="C150">
-        <v>982.07</v>
+        <v>895.24</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46134</v>
+        <v>46124</v>
       </c>
       <c r="B151" t="s">
         <v>5</v>
       </c>
       <c r="C151">
-        <v>1110.42</v>
+        <v>1014.46</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46135</v>
+        <v>46125</v>
       </c>
       <c r="B152" t="s">
         <v>5</v>
       </c>
       <c r="C152">
-        <v>1022.98</v>
+        <v>772.98</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46136</v>
+        <v>46126</v>
       </c>
       <c r="B153" t="s">
         <v>5</v>
       </c>
       <c r="C153">
-        <v>1204.6300000000001</v>
+        <v>1057.8800000000001</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46137</v>
+        <v>46127</v>
       </c>
       <c r="B154" t="s">
         <v>5</v>
       </c>
       <c r="C154">
-        <v>1144.56</v>
+        <v>869.45</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46138</v>
+        <v>46128</v>
       </c>
       <c r="B155" t="s">
         <v>5</v>
       </c>
       <c r="C155">
-        <v>990.51</v>
+        <v>845.41</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46139</v>
+        <v>46129</v>
       </c>
       <c r="B156" t="s">
         <v>5</v>
       </c>
       <c r="C156">
-        <v>754.98</v>
+        <v>863.08</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46140</v>
+        <v>46130</v>
       </c>
       <c r="B157" t="s">
         <v>5</v>
       </c>
       <c r="C157">
-        <v>758.6</v>
+        <v>973.22</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46141</v>
+        <v>46131</v>
       </c>
       <c r="B158" t="s">
         <v>5</v>
       </c>
       <c r="C158">
-        <v>759.8</v>
+        <v>1320.17</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46142</v>
+        <v>46132</v>
       </c>
       <c r="B159" t="s">
         <v>5</v>
       </c>
       <c r="C159">
-        <v>741.82</v>
+        <v>916.68</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B160" t="s">
         <v>5</v>
       </c>
       <c r="C160">
-        <v>647.97</v>
+        <v>982.07</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46144</v>
+        <v>46134</v>
       </c>
       <c r="B161" t="s">
         <v>5</v>
       </c>
       <c r="C161">
-        <v>811.24</v>
+        <v>1110.42</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46145</v>
+        <v>46135</v>
       </c>
       <c r="B162" t="s">
         <v>5</v>
       </c>
       <c r="C162">
-        <v>1538.71</v>
+        <v>1022.98</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46146</v>
+        <v>46136</v>
       </c>
       <c r="B163" t="s">
         <v>5</v>
       </c>
       <c r="C163">
-        <v>1123.06</v>
+        <v>1204.6300000000001</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46147</v>
+        <v>46137</v>
       </c>
       <c r="B164" t="s">
         <v>5</v>
       </c>
       <c r="C164">
-        <v>1014.45</v>
+        <v>1144.56</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46148</v>
+        <v>46138</v>
       </c>
       <c r="B165" t="s">
         <v>5</v>
       </c>
       <c r="C165">
-        <v>860.07</v>
+        <v>990.51</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46149</v>
+        <v>46139</v>
       </c>
       <c r="B166" t="s">
         <v>5</v>
       </c>
       <c r="C166">
-        <v>945.18</v>
+        <v>754.98</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46150</v>
+        <v>46140</v>
       </c>
       <c r="B167" t="s">
         <v>5</v>
       </c>
       <c r="C167">
-        <v>1119.22</v>
+        <v>758.6</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46151</v>
+        <v>46141</v>
       </c>
       <c r="B168" t="s">
         <v>5</v>
       </c>
       <c r="C168">
-        <v>1132.57</v>
+        <v>759.8</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46152</v>
+        <v>46142</v>
       </c>
       <c r="B169" t="s">
         <v>5</v>
       </c>
       <c r="C169">
-        <v>927.5</v>
+        <v>741.82</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="B170" t="s">
         <v>5</v>
       </c>
       <c r="C170">
-        <v>898.93</v>
+        <v>647.97</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46154</v>
+        <v>46144</v>
       </c>
       <c r="B171" t="s">
         <v>5</v>
       </c>
       <c r="C171">
-        <v>903.1</v>
+        <v>811.24</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46155</v>
+        <v>46145</v>
       </c>
       <c r="B172" t="s">
         <v>5</v>
       </c>
       <c r="C172">
-        <v>921.23</v>
+        <v>1538.71</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="B173" t="s">
         <v>5</v>
       </c>
       <c r="C173">
-        <v>974.18</v>
+        <v>1123.06</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46157</v>
+        <v>46147</v>
       </c>
       <c r="B174" t="s">
         <v>5</v>
       </c>
       <c r="C174">
-        <v>1418.86</v>
+        <v>1014.45</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46158</v>
+        <v>46148</v>
       </c>
       <c r="B175" t="s">
         <v>5</v>
       </c>
       <c r="C175">
-        <v>978.18</v>
+        <v>860.07</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46159</v>
+        <v>46149</v>
       </c>
       <c r="B176" t="s">
         <v>5</v>
       </c>
       <c r="C176">
-        <v>964.8</v>
+        <v>945.18</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="B177" t="s">
         <v>5</v>
       </c>
       <c r="C177">
-        <v>911.14</v>
+        <v>1119.22</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46161</v>
+        <v>46151</v>
       </c>
       <c r="B178" t="s">
         <v>5</v>
       </c>
       <c r="C178">
-        <v>1006.19</v>
+        <v>1132.57</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46162</v>
+        <v>46152</v>
       </c>
       <c r="B179" t="s">
         <v>5</v>
       </c>
       <c r="C179">
-        <v>933.57</v>
+        <v>927.5</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B180" t="s">
         <v>5</v>
       </c>
       <c r="C180">
-        <v>961.02</v>
+        <v>898.93</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B181" t="s">
         <v>5</v>
       </c>
       <c r="C181">
-        <v>983.94</v>
+        <v>903.1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46165</v>
+        <v>46155</v>
       </c>
       <c r="B182" t="s">
         <v>5</v>
       </c>
       <c r="C182">
-        <v>960.65</v>
+        <v>921.23</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46166</v>
+        <v>46156</v>
       </c>
       <c r="B183" t="s">
         <v>5</v>
       </c>
       <c r="C183">
-        <v>1083.08</v>
+        <v>974.18</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B184" t="s">
         <v>5</v>
       </c>
       <c r="C184">
-        <v>884.8</v>
+        <v>1418.86</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46168</v>
+        <v>46158</v>
       </c>
       <c r="B185" t="s">
         <v>5</v>
       </c>
       <c r="C185">
-        <v>834.89</v>
+        <v>978.18</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46169</v>
+        <v>46159</v>
       </c>
       <c r="B186" t="s">
         <v>5</v>
       </c>
       <c r="C186">
-        <v>895.54</v>
+        <v>964.8</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B187" t="s">
         <v>5</v>
       </c>
       <c r="C187">
-        <v>924.29</v>
+        <v>911.14</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B188" t="s">
         <v>5</v>
       </c>
       <c r="C188">
-        <v>932.33</v>
+        <v>1006.19</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>46172</v>
+        <v>46162</v>
       </c>
       <c r="B189" t="s">
         <v>5</v>
       </c>
       <c r="C189">
-        <v>994.71</v>
+        <v>933.57</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>46173</v>
+        <v>46163</v>
       </c>
       <c r="B190" t="s">
         <v>5</v>
       </c>
       <c r="C190">
-        <v>915.54</v>
+        <v>961.02</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B191" t="s">
         <v>5</v>
       </c>
       <c r="C191">
-        <v>767.55</v>
+        <v>983.94</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
-        <v>46175</v>
+        <v>46165</v>
       </c>
       <c r="B192" t="s">
         <v>5</v>
       </c>
       <c r="C192">
-        <v>1034.02</v>
+        <v>960.65</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
-        <v>46176</v>
+        <v>46166</v>
       </c>
       <c r="B193" t="s">
         <v>5</v>
       </c>
       <c r="C193">
-        <v>1324.51</v>
+        <v>1083.08</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B194" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C194">
-        <v>3125.43</v>
+        <v>884.8</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B195" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C195">
-        <v>2189.2600000000002</v>
+        <v>834.89</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
-        <v>46179</v>
+        <v>46169</v>
       </c>
       <c r="B196" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C196">
-        <v>1761.01</v>
+        <v>895.54</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
-        <v>46180</v>
+        <v>46170</v>
       </c>
       <c r="B197" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C197">
-        <v>1829.97</v>
+        <v>924.29</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C198">
-        <v>895.72</v>
+        <v>932.33</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
-        <v>46178</v>
+        <v>46172</v>
       </c>
       <c r="B199" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C199">
-        <v>836.49</v>
+        <v>994.71</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
-        <v>46179</v>
+        <v>46173</v>
       </c>
       <c r="B200" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C200">
-        <v>1521.28</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
-        <v>46180</v>
+        <v>46174</v>
       </c>
       <c r="B201" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C201">
-        <v>1212.58</v>
+        <v>767.55</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B202" t="s">
         <v>5</v>
       </c>
       <c r="C202">
-        <v>1059.71</v>
+        <v>1034.02</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B203" t="s">
         <v>5</v>
       </c>
       <c r="C203">
-        <v>1076.56</v>
+        <v>1324.51</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="B204" t="s">
         <v>5</v>
       </c>
       <c r="C204">
-        <v>1098.32</v>
+        <v>1059.71</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
-        <v>46180</v>
+        <v>46178</v>
       </c>
       <c r="B205" t="s">
         <v>5</v>
       </c>
       <c r="C205">
-        <v>1111.45</v>
+        <v>1076.56</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
-        <v>46181</v>
+        <v>46179</v>
       </c>
       <c r="B206" t="s">
         <v>5</v>
       </c>
       <c r="C206">
-        <v>864.33</v>
+        <v>1095.47</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="B207" t="s">
         <v>5</v>
       </c>
       <c r="C207">
-        <v>1026.04</v>
+        <v>1111.45</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -2741,10 +2751,10 @@
         <v>46181</v>
       </c>
       <c r="B208" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C208">
-        <v>2359.3000000000002</v>
+        <v>863.95</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
@@ -2752,2504 +2762,2183 @@
         <v>46182</v>
       </c>
       <c r="B209" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C209">
-        <v>2688.85</v>
+        <v>1026.04</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B210" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C210">
-        <v>981.26</v>
+        <v>1100.55</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B211" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C211">
-        <v>1002.08</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B212" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C212">
-        <v>2818.5</v>
+        <v>820.13</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B213" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C213">
-        <v>1690.68</v>
+        <v>1053.48</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="B214" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C214">
-        <v>997.2</v>
+        <v>1377.55</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B215" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C215">
-        <v>822.2</v>
+        <v>1001.64</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B216" t="s">
         <v>5</v>
       </c>
       <c r="C216">
-        <v>1100.55</v>
+        <v>900.81</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C217">
-        <v>1007.25</v>
+        <v>337.24</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B218" t="s">
+        <v>13</v>
+      </c>
+      <c r="C218">
+        <v>491.46</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B219" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219">
+        <v>727.09</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220">
+        <v>918.2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B221" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221">
+        <v>959.32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C211" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>462.62</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>1266.31</v>
+      <c r="C3" s="2">
+        <v>3441.39</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>467.84</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>521.47</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>1284.17</v>
+      <c r="C6" s="2">
+        <v>3221.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>500.73</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>516.37</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>1359.4</v>
+      <c r="C9" s="2">
+        <v>3276.72</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>504.72</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46173</v>
+        <v>46187</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>528.64</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46173</v>
+        <v>46187</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="C12">
-        <v>1335.7</v>
+      <c r="C12" s="2">
+        <v>3486.04</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46173</v>
+        <v>46187</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>529.03</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46172</v>
+        <v>46186</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>509.86</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46172</v>
+        <v>46186</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
-      <c r="C15">
-        <v>1322.84</v>
+      <c r="C15" s="2">
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46172</v>
+        <v>46186</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>502.21</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>500.59</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C18">
-        <v>1254.29</v>
+      <c r="C18" s="2">
+        <v>3072.14</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>508.81</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>499.91</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="C21">
-        <v>1248.17</v>
+      <c r="C21" s="2">
+        <v>3183.11</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>514.72</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>505.09</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="C24">
-        <v>1136.27</v>
+      <c r="C24" s="2">
+        <v>2587.6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>539.37</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>507.95</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27">
-        <v>1173.17</v>
+      <c r="C27" s="2">
+        <v>3838.27</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>523.91999999999996</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>451.19</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
-      <c r="C30">
-        <v>720.79</v>
+      <c r="C30" s="2">
+        <v>2990.38</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>429.65</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46166</v>
+        <v>46180</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>524.41999999999996</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46166</v>
+        <v>46180</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
-      <c r="C33">
-        <v>705.94</v>
+      <c r="C33" s="2">
+        <v>1448.25</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46166</v>
+        <v>46180</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>479.73</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>439.45</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
-      <c r="C36">
-        <v>663.05</v>
+      <c r="C36" s="2">
+        <v>1318.78</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>509.26</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>447.4</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
-      <c r="C39">
-        <v>692.07</v>
+      <c r="C39" s="2">
+        <v>1276.5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>446.07</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>466.82</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
-      <c r="C42">
-        <v>669.52</v>
+      <c r="C42" s="2">
+        <v>1257.7</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43">
-        <v>403.4</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>471.71</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
-      <c r="C45">
-        <v>659.67</v>
+      <c r="C45" s="2">
+        <v>1267.75</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>486.91</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>562.97</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
-      <c r="C48">
-        <v>703.37</v>
+      <c r="C48" s="2">
+        <v>1284.17</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C49">
-        <v>532.58000000000004</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C50">
-        <v>506.5</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
-      <c r="C51">
-        <v>668.52</v>
+      <c r="C51" s="2">
+        <v>1359.4</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>505.15</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C53">
-        <v>582.09</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
-      <c r="C54">
-        <v>570.80999999999995</v>
+      <c r="C54" s="2">
+        <v>1335.7</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>571.26</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>454.06</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
-      <c r="C57">
-        <v>420.48</v>
+      <c r="C57" s="2">
+        <v>1322.84</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>449.56</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>487.21</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
-      <c r="C60">
-        <v>493.46</v>
+      <c r="C60" s="2">
+        <v>1254.29</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C61">
-        <v>505.54</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C62">
-        <v>591.13</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
-      <c r="C63">
-        <v>570.92999999999995</v>
+      <c r="C63" s="2">
+        <v>1248.17</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C64">
-        <v>579.72</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C65">
-        <v>537.16999999999996</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
-      <c r="C66">
-        <v>547.42999999999995</v>
+      <c r="C66" s="2">
+        <v>1136.27</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C67">
-        <v>531.26</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C68">
-        <v>506.59</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
-      <c r="C69">
-        <v>516.32000000000005</v>
+      <c r="C69" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C70">
-        <v>512.42999999999995</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C71">
-        <v>451.42</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>477.63</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C73">
-        <v>480.14</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>471.83</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>473.37</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C76">
-        <v>440.24</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C77">
-        <v>399.36</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>457.2</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C79">
-        <v>413.27</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C80">
-        <v>429.68</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
       <c r="C81">
-        <v>458.96</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C82">
-        <v>576.4</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C83">
-        <v>446.33</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
       <c r="C84">
-        <v>462.4</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C85">
-        <v>469.28</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C86">
-        <v>492.66</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
       <c r="C87">
-        <v>524.33000000000004</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88">
-        <v>514.92999999999995</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C89">
-        <v>516.41999999999996</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
       </c>
       <c r="C90">
-        <v>555.08000000000004</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91">
-        <v>525.04</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C92">
-        <v>646.28</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>544.63</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="B94" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C94">
-        <v>529.30999999999995</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C95">
-        <v>566.66</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>496.42</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C97">
-        <v>467.75</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C98">
-        <v>507.5</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>468.24</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C100">
-        <v>435.83</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C101">
-        <v>490.51</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>442.08</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>513.24</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46142</v>
+        <v>46156</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C104">
-        <v>490.96</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46142</v>
+        <v>46156</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>390.46</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46142</v>
+        <v>46156</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C106">
-        <v>455.23</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C107">
-        <v>517.11</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>473.63</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C109">
-        <v>416.64</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C110">
-        <v>557.57000000000005</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>633.22</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C112">
-        <v>481.26</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C113">
-        <v>508.81</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114">
-        <v>600.36</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>595.71</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C116">
-        <v>427.5</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>490.83</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118">
-        <v>598.64</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C119">
-        <v>184.94</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>333.98</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="B121" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121">
-        <v>270.85000000000002</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C122">
-        <v>284.88</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123">
-        <v>270.06</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="B124" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C124">
-        <v>296.23</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C125">
-        <v>713.78</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="B126" t="s">
         <v>3</v>
       </c>
       <c r="C126">
-        <v>606.85</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>336.5</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C128">
-        <v>509.61</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>536.29</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C130">
-        <v>766.34</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46133</v>
+        <v>46147</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46133</v>
+        <v>46147</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46133</v>
+        <v>46147</v>
       </c>
       <c r="B133" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C133">
-        <v>750.08</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B136" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C136">
-        <v>313.98</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="B139" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46130</v>
+        <v>46144</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46130</v>
+        <v>46144</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46130</v>
+        <v>46144</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46129</v>
+        <v>46143</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46129</v>
+        <v>46143</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46129</v>
+        <v>46143</v>
       </c>
       <c r="B145" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46124</v>
+        <v>46138</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46124</v>
+        <v>46138</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46124</v>
+        <v>46138</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="B163" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>284.88</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>336.5</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>606.85</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>713.78</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>766.34</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>536.29</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>509.61</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46119</v>
+        <v>46133</v>
       </c>
       <c r="B173" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>750.08</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46119</v>
+        <v>46132</v>
       </c>
       <c r="B174" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>313.98</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="1">
-        <v>46119</v>
-      </c>
-      <c r="B175" t="s">
-        <v>10</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
-      </c>
+      <c r="A175" s="1"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B176" t="s">
-        <v>9</v>
-      </c>
-      <c r="C176">
-        <v>0</v>
-      </c>
+      <c r="A176" s="1"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B177" t="s">
-        <v>3</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
-      </c>
+      <c r="A177" s="1"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B178" t="s">
-        <v>10</v>
-      </c>
-      <c r="C178">
-        <v>0</v>
-      </c>
+      <c r="A178" s="1"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B179" t="s">
-        <v>9</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
-      </c>
+      <c r="A179" s="1"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B180" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
-      </c>
+      <c r="A180" s="1"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B181" t="s">
-        <v>10</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
+      <c r="A181" s="1"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="1">
-        <v>46116</v>
-      </c>
-      <c r="B182" t="s">
-        <v>9</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
+      <c r="A182" s="1"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="1">
-        <v>46116</v>
-      </c>
-      <c r="B183" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
+      <c r="A183" s="1"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" s="1">
-        <v>46116</v>
-      </c>
-      <c r="B184" t="s">
-        <v>10</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
-      </c>
+      <c r="A184" s="1"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" s="1">
-        <v>46115</v>
-      </c>
-      <c r="B185" t="s">
-        <v>9</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
+      <c r="A185" s="1"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" s="1">
-        <v>46115</v>
-      </c>
-      <c r="B186" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
-      </c>
+      <c r="A186" s="1"/>
+      <c r="C186" s="2"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" s="1">
-        <v>46115</v>
-      </c>
-      <c r="B187" t="s">
-        <v>10</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
+      <c r="A187" s="1"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B188" t="s">
-        <v>9</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
+      <c r="A188" s="1"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B189" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
+      <c r="A189" s="1"/>
+      <c r="C189" s="2"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B190" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
+      <c r="A190" s="1"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" s="1">
-        <v>46113</v>
-      </c>
-      <c r="B191" t="s">
-        <v>9</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
+      <c r="A191" s="1"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" s="1">
-        <v>46113</v>
-      </c>
-      <c r="B192" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
+      <c r="A192" s="1"/>
+      <c r="C192" s="2"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" s="1">
-        <v>46113</v>
-      </c>
-      <c r="B193" t="s">
-        <v>10</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
-      </c>
+      <c r="A193" s="1"/>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" s="1">
-        <v>46180</v>
-      </c>
-      <c r="B194" t="s">
-        <v>10</v>
-      </c>
-      <c r="C194">
-        <v>549.6</v>
-      </c>
+      <c r="A194" s="1"/>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" s="1">
-        <v>46180</v>
-      </c>
-      <c r="B195" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="2">
-        <v>1442.5</v>
-      </c>
+      <c r="A195" s="1"/>
+      <c r="C195" s="2"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" s="1">
-        <v>46180</v>
-      </c>
-      <c r="B196" t="s">
-        <v>9</v>
-      </c>
-      <c r="C196">
-        <v>530.62</v>
-      </c>
+      <c r="A196" s="1"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" s="1">
-        <v>46179</v>
-      </c>
-      <c r="B197" t="s">
-        <v>10</v>
-      </c>
-      <c r="C197">
-        <v>496.91</v>
-      </c>
+      <c r="A197" s="1"/>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" s="1">
-        <v>46179</v>
-      </c>
-      <c r="B198" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="2">
-        <v>1318.78</v>
-      </c>
+      <c r="A198" s="1"/>
+      <c r="C198" s="2"/>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" s="1">
-        <v>46179</v>
-      </c>
-      <c r="B199" t="s">
-        <v>9</v>
-      </c>
-      <c r="C199">
-        <v>492.79</v>
-      </c>
+      <c r="A199" s="1"/>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" s="1">
-        <v>46178</v>
-      </c>
-      <c r="B200" t="s">
-        <v>10</v>
-      </c>
-      <c r="C200">
-        <v>493.28</v>
-      </c>
+      <c r="A200" s="1"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" s="1">
-        <v>46178</v>
-      </c>
-      <c r="B201" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="2">
-        <v>1276.5</v>
-      </c>
+      <c r="A201" s="1"/>
+      <c r="C201" s="2"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" s="1">
-        <v>46178</v>
-      </c>
-      <c r="B202" t="s">
-        <v>9</v>
-      </c>
-      <c r="C202">
-        <v>467.42</v>
-      </c>
+      <c r="A202" s="1"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" s="1">
-        <v>46177</v>
-      </c>
-      <c r="B203" t="s">
-        <v>10</v>
-      </c>
-      <c r="C203">
-        <v>505.85</v>
-      </c>
+      <c r="A203" s="1"/>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" s="1">
-        <v>46177</v>
-      </c>
-      <c r="B204" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="2">
-        <v>1257.7</v>
-      </c>
+      <c r="A204" s="1"/>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" s="1">
-        <v>46177</v>
-      </c>
-      <c r="B205" t="s">
-        <v>9</v>
-      </c>
-      <c r="C205">
-        <v>509.16</v>
-      </c>
+      <c r="A205" s="1"/>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="1">
-        <v>46182</v>
-      </c>
-      <c r="B206" t="s">
-        <v>10</v>
-      </c>
-      <c r="C206">
-        <v>505.03</v>
-      </c>
+      <c r="A206" s="1"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="1">
-        <v>46182</v>
-      </c>
-      <c r="B207" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="2">
-        <v>3828.32</v>
-      </c>
+      <c r="A207" s="1"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="1">
-        <v>46182</v>
-      </c>
-      <c r="B208" t="s">
-        <v>9</v>
-      </c>
-      <c r="C208">
-        <v>476.31</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209" s="1">
-        <v>46181</v>
-      </c>
-      <c r="B209" t="s">
-        <v>10</v>
-      </c>
-      <c r="C209">
-        <v>492.98</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" s="1">
-        <v>46181</v>
-      </c>
-      <c r="B210" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="2">
-        <v>2990.38</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211" s="1">
-        <v>46181</v>
-      </c>
-      <c r="B211" t="s">
-        <v>9</v>
-      </c>
-      <c r="C211">
-        <v>512.59</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" s="1">
-        <v>46184</v>
-      </c>
-      <c r="B212" t="s">
-        <v>9</v>
-      </c>
-      <c r="C212">
-        <v>505.51</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A213" s="1">
-        <v>46184</v>
-      </c>
-      <c r="B213" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213">
-        <v>3168.19</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" s="1">
-        <v>46184</v>
-      </c>
-      <c r="B214" t="s">
-        <v>10</v>
-      </c>
-      <c r="C214">
-        <v>505.17</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215" s="1">
-        <v>46183</v>
-      </c>
-      <c r="B215" t="s">
-        <v>9</v>
-      </c>
-      <c r="C215">
-        <v>458.08</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" s="1">
-        <v>46183</v>
-      </c>
-      <c r="B216" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216">
-        <v>2587.6</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217" s="1">
-        <v>46183</v>
-      </c>
-      <c r="B217" t="s">
-        <v>10</v>
-      </c>
-      <c r="C217">
-        <v>493.44</v>
-      </c>
+      <c r="A208" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C174" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78EA88C-3D1A-4718-85C2-42C3A362F786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4A40DD-D613-4159-B18A-1C0B003F29DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
     <sheet name="FB" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$174</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="15">
   <si>
     <t>Day</t>
   </si>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C221"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -482,79 +482,79 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46189</v>
+        <v>46118</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>79.209999999999994</v>
+        <v>876.13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46186</v>
+        <v>46119</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>521.09</v>
+        <v>1522.15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46187</v>
+        <v>46120</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1197.73</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46188</v>
+        <v>46120</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>778.85</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46189</v>
+        <v>46120</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>617.65</v>
+        <v>1482.18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46183</v>
+        <v>46121</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>298.89</v>
+        <v>628.70000000000005</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>64.97</v>
+        <v>1029.69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -562,10 +562,10 @@
         <v>46121</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>628.70000000000005</v>
+        <v>997.89</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -581,1124 +581,1124 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46123</v>
+        <v>46122</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>374.88</v>
+        <v>663.55</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46124</v>
+        <v>46122</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>532.29999999999995</v>
+        <v>1000.12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46125</v>
+        <v>46123</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13">
-        <v>620.17999999999995</v>
+        <v>374.88</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46126</v>
+        <v>46123</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>1437.37</v>
+        <v>373.1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46127</v>
+        <v>46123</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>1094.69</v>
+        <v>895.24</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46128</v>
+        <v>46124</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16">
-        <v>911.37</v>
+        <v>532.29999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46129</v>
+        <v>46124</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>1061.49</v>
+        <v>595.20000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46130</v>
+        <v>46124</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>1085.51</v>
+        <v>1014.46</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46131</v>
+        <v>46125</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19">
-        <v>999.47</v>
+        <v>620.17999999999995</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>975.32</v>
+        <v>625.48</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>1047.22</v>
+        <v>772.98</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46134</v>
+        <v>46126</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22">
-        <v>1259.8699999999999</v>
+        <v>1437.37</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46135</v>
+        <v>46126</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>1064.55</v>
+        <v>1455.55</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46136</v>
+        <v>46126</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>996.48</v>
+        <v>1057.8800000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46137</v>
+        <v>46127</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25">
-        <v>1312.03</v>
+        <v>1094.69</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46138</v>
+        <v>46127</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>1028.4100000000001</v>
+        <v>980.89</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46139</v>
+        <v>46127</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>788.39</v>
+        <v>869.45</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46140</v>
+        <v>46128</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28">
-        <v>773.31</v>
+        <v>911.37</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>773.36</v>
+        <v>1020.87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46142</v>
+        <v>46128</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>776.21</v>
+        <v>845.41</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46143</v>
+        <v>46129</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31">
-        <v>896.44</v>
+        <v>1061.49</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46144</v>
+        <v>46129</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>977.68</v>
+        <v>1074.21</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46145</v>
+        <v>46129</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>1365.79</v>
+        <v>863.08</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46146</v>
+        <v>46130</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34">
-        <v>883.13</v>
+        <v>1085.51</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46147</v>
+        <v>46130</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>885.01</v>
+        <v>1063.98</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46148</v>
+        <v>46130</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>771.48</v>
+        <v>973.22</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46149</v>
+        <v>46131</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37">
-        <v>1129.58</v>
+        <v>999.47</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46150</v>
+        <v>46131</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>1237.75</v>
+        <v>1040.55</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46151</v>
+        <v>46131</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>1036.03</v>
+        <v>1320.17</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46152</v>
+        <v>46132</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
       </c>
       <c r="C40">
-        <v>1041.58</v>
+        <v>975.32</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>1050.2</v>
+        <v>992.2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46154</v>
+        <v>46132</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C42">
-        <v>963.55</v>
+        <v>916.68</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46155</v>
+        <v>46133</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
       </c>
       <c r="C43">
-        <v>852.6</v>
+        <v>1047.22</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46156</v>
+        <v>46133</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>929.18</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46157</v>
+        <v>46133</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>1007.08</v>
+        <v>982.07</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46158</v>
+        <v>46134</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46">
-        <v>1190.55</v>
+        <v>1259.8699999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46159</v>
+        <v>46134</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>1025.94</v>
+        <v>1249.56</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46160</v>
+        <v>46134</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>883.7</v>
+        <v>1110.42</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46135</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
       </c>
       <c r="C49">
-        <v>822.74</v>
+        <v>1064.55</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46162</v>
+        <v>46135</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>889.78</v>
+        <v>1047.03</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46163</v>
+        <v>46135</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>1238.71</v>
+        <v>1022.98</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46164</v>
+        <v>46136</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
       </c>
       <c r="C52">
-        <v>960.3</v>
+        <v>996.48</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46165</v>
+        <v>46136</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>1035.1300000000001</v>
+        <v>1220.19</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46166</v>
+        <v>46136</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>935.29</v>
+        <v>1204.6300000000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46167</v>
+        <v>46137</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
       </c>
       <c r="C55">
-        <v>1300.27</v>
+        <v>1312.03</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46168</v>
+        <v>46137</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>1691.22</v>
+        <v>1267.83</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46169</v>
+        <v>46137</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>1719.87</v>
+        <v>1144.56</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46170</v>
+        <v>46138</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58">
-        <v>1581.56</v>
+        <v>1028.4100000000001</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46171</v>
+        <v>46138</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>1577.46</v>
+        <v>1000.43</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46172</v>
+        <v>46138</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C60">
-        <v>1602.4</v>
+        <v>990.51</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46173</v>
+        <v>46139</v>
       </c>
       <c r="B61" t="s">
         <v>8</v>
       </c>
       <c r="C61">
-        <v>1425.5</v>
+        <v>788.39</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>853.4</v>
+        <v>750.37</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46176</v>
+        <v>46139</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C63">
-        <v>576.04</v>
+        <v>754.98</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46177</v>
+        <v>46140</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
       </c>
       <c r="C64">
-        <v>3125.43</v>
+        <v>773.31</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46178</v>
+        <v>46140</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C65">
-        <v>2189.2600000000002</v>
+        <v>750.11</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46179</v>
+        <v>46140</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>1761.01</v>
+        <v>758.6</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46180</v>
+        <v>46141</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
       </c>
       <c r="C67">
-        <v>1829.97</v>
+        <v>773.36</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46181</v>
+        <v>46141</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C68">
-        <v>2359.3000000000002</v>
+        <v>749.15</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46182</v>
+        <v>46141</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C69">
-        <v>2694.6</v>
+        <v>759.8</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46183</v>
+        <v>46142</v>
       </c>
       <c r="B70" t="s">
         <v>8</v>
       </c>
       <c r="C70">
-        <v>2818.5</v>
+        <v>776.21</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46184</v>
+        <v>46142</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>1690.68</v>
+        <v>750.4</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46185</v>
+        <v>46142</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C72">
-        <v>911.1</v>
+        <v>741.82</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46186</v>
+        <v>46143</v>
       </c>
       <c r="B73" t="s">
         <v>8</v>
       </c>
       <c r="C73">
-        <v>803.62</v>
+        <v>896.44</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46187</v>
+        <v>46143</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C74">
-        <v>656.27</v>
+        <v>733.27</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="B75" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C75">
-        <v>679.73</v>
+        <v>647.97</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46189</v>
+        <v>46144</v>
       </c>
       <c r="B76" t="s">
         <v>8</v>
       </c>
       <c r="C76">
-        <v>879.71</v>
+        <v>977.68</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46120</v>
+        <v>46144</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>31.83</v>
+        <v>1008.56</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46121</v>
+        <v>46144</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C78">
-        <v>1029.69</v>
+        <v>811.24</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46122</v>
+        <v>46145</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C79">
-        <v>663.55</v>
+        <v>1365.79</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46123</v>
+        <v>46145</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
-        <v>373.1</v>
+        <v>1267.73</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46124</v>
+        <v>46145</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81">
-        <v>595.20000000000005</v>
+        <v>1538.71</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C82">
-        <v>625.48</v>
+        <v>883.13</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46126</v>
+        <v>46146</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>1455.55</v>
+        <v>1106.75</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46127</v>
+        <v>46146</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C84">
-        <v>980.89</v>
+        <v>1123.06</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46128</v>
+        <v>46147</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C85">
-        <v>1020.87</v>
+        <v>885.01</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46129</v>
+        <v>46147</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>1074.21</v>
+        <v>1012.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46130</v>
+        <v>46147</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C87">
-        <v>1063.98</v>
+        <v>1014.45</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46131</v>
+        <v>46148</v>
       </c>
       <c r="B88" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C88">
-        <v>1040.55</v>
+        <v>771.48</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46132</v>
+        <v>46148</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>992.2</v>
+        <v>743.27</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46133</v>
+        <v>46148</v>
       </c>
       <c r="B90" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90">
-        <v>962.16</v>
+        <v>860.07</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46134</v>
+        <v>46149</v>
       </c>
       <c r="B91" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C91">
-        <v>1249.56</v>
+        <v>1129.58</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
-        <v>1047.03</v>
+        <v>1104.6600000000001</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93">
-        <v>1220.19</v>
+        <v>945.18</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46137</v>
+        <v>46150</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>1267.83</v>
+        <v>1237.75</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46138</v>
+        <v>46150</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>1000.43</v>
+        <v>1062.3499999999999</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C96">
-        <v>750.37</v>
+        <v>1119.22</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46140</v>
+        <v>46151</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C97">
-        <v>750.11</v>
+        <v>1036.03</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46141</v>
+        <v>46151</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
       <c r="C98">
-        <v>749.15</v>
+        <v>1075.5</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46142</v>
+        <v>46151</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>750.4</v>
+        <v>1132.57</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46143</v>
+        <v>46152</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C100">
-        <v>733.27</v>
+        <v>1041.58</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
       <c r="C101">
-        <v>1008.56</v>
+        <v>924.44</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102">
-        <v>1267.73</v>
+        <v>927.5</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C103">
-        <v>1106.75</v>
+        <v>1050.2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
       <c r="C104">
-        <v>1012.99</v>
+        <v>976.86</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>743.27</v>
+        <v>898.93</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="B106" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C106">
-        <v>1104.6600000000001</v>
+        <v>963.55</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107">
-        <v>1062.3499999999999</v>
+        <v>981.19</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>1075.5</v>
+        <v>903.1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C109">
-        <v>924.44</v>
+        <v>852.6</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110">
-        <v>976.86</v>
+        <v>1026.52</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>981.19</v>
+        <v>921.23</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B112" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C112">
-        <v>1026.52</v>
+        <v>929.18</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -1714,1124 +1714,1124 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114">
-        <v>1097.79</v>
+        <v>974.18</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="B115" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C115">
-        <v>862.95</v>
+        <v>1007.08</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46159</v>
+        <v>46157</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116">
-        <v>1015.09</v>
+        <v>1097.79</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B117" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C117">
-        <v>1062.22</v>
+        <v>1418.86</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46161</v>
+        <v>46158</v>
       </c>
       <c r="B118" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C118">
-        <v>988.49</v>
+        <v>1190.55</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46162</v>
+        <v>46158</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119">
-        <v>778.96</v>
+        <v>862.95</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46163</v>
+        <v>46158</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C120">
-        <v>856.43</v>
+        <v>978.18</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46164</v>
+        <v>46159</v>
       </c>
       <c r="B121" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C121">
-        <v>1182.79</v>
+        <v>1025.94</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46165</v>
+        <v>46159</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122">
-        <v>1057.1099999999999</v>
+        <v>1015.09</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46166</v>
+        <v>46159</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C123">
-        <v>966.22</v>
+        <v>964.8</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="B124" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C124">
-        <v>934.12</v>
+        <v>883.7</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
       <c r="C125">
-        <v>890.5</v>
+        <v>1062.22</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B126" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C126">
-        <v>833.8</v>
+        <v>911.14</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C127">
-        <v>872.27</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
       <c r="C128">
-        <v>979.23</v>
+        <v>988.49</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46172</v>
+        <v>46161</v>
       </c>
       <c r="B129" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C129">
-        <v>960.49</v>
+        <v>1006.19</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46173</v>
+        <v>46162</v>
       </c>
       <c r="B130" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C130">
-        <v>930.07</v>
+        <v>889.78</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
       <c r="C131">
-        <v>897.07</v>
+        <v>778.96</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46175</v>
+        <v>46162</v>
       </c>
       <c r="B132" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C132">
-        <v>1158.77</v>
+        <v>933.57</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46176</v>
+        <v>46163</v>
       </c>
       <c r="B133" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C133">
-        <v>1026.26</v>
+        <v>1238.71</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46177</v>
+        <v>46163</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
       <c r="C134">
-        <v>895.72</v>
+        <v>856.43</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46178</v>
+        <v>46163</v>
       </c>
       <c r="B135" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C135">
-        <v>836.49</v>
+        <v>961.02</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46179</v>
+        <v>46164</v>
       </c>
       <c r="B136" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C136">
-        <v>1521.28</v>
+        <v>960.3</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46180</v>
+        <v>46164</v>
       </c>
       <c r="B137" t="s">
         <v>4</v>
       </c>
       <c r="C137">
-        <v>1212.58</v>
+        <v>1182.79</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="B138" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C138">
-        <v>981.26</v>
+        <v>983.94</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46182</v>
+        <v>46165</v>
       </c>
       <c r="B139" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C139">
-        <v>1002.08</v>
+        <v>1035.1300000000001</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46183</v>
+        <v>46165</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
       <c r="C140">
-        <v>997.2</v>
+        <v>1057.1099999999999</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46184</v>
+        <v>46165</v>
       </c>
       <c r="B141" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C141">
-        <v>822.2</v>
+        <v>960.65</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46185</v>
+        <v>46166</v>
       </c>
       <c r="B142" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C142">
-        <v>669.78</v>
+        <v>935.29</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46186</v>
+        <v>46166</v>
       </c>
       <c r="B143" t="s">
         <v>4</v>
       </c>
       <c r="C143">
-        <v>1208.0999999999999</v>
+        <v>966.22</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46187</v>
+        <v>46166</v>
       </c>
       <c r="B144" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144">
-        <v>1582.98</v>
+        <v>1083.08</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="B145" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C145">
-        <v>931.83</v>
+        <v>1300.27</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="B146" t="s">
         <v>4</v>
       </c>
       <c r="C146">
-        <v>920.5</v>
+        <v>934.12</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="B147" t="s">
         <v>5</v>
       </c>
       <c r="C147">
-        <v>1482.18</v>
+        <v>884.8</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46121</v>
+        <v>46168</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C148">
-        <v>997.89</v>
+        <v>1691.22</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46122</v>
+        <v>46168</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149">
-        <v>1000.12</v>
+        <v>890.5</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46123</v>
+        <v>46168</v>
       </c>
       <c r="B150" t="s">
         <v>5</v>
       </c>
       <c r="C150">
-        <v>895.24</v>
+        <v>834.89</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46124</v>
+        <v>46169</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C151">
-        <v>1014.46</v>
+        <v>1719.87</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46125</v>
+        <v>46169</v>
       </c>
       <c r="B152" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152">
-        <v>772.98</v>
+        <v>833.8</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46126</v>
+        <v>46169</v>
       </c>
       <c r="B153" t="s">
         <v>5</v>
       </c>
       <c r="C153">
-        <v>1057.8800000000001</v>
+        <v>895.54</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46127</v>
+        <v>46170</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C154">
-        <v>869.45</v>
+        <v>1581.56</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46128</v>
+        <v>46170</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155">
-        <v>845.41</v>
+        <v>872.27</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46129</v>
+        <v>46170</v>
       </c>
       <c r="B156" t="s">
         <v>5</v>
       </c>
       <c r="C156">
-        <v>863.08</v>
+        <v>924.29</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46130</v>
+        <v>46171</v>
       </c>
       <c r="B157" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C157">
-        <v>973.22</v>
+        <v>1577.46</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46131</v>
+        <v>46171</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>1320.17</v>
+        <v>979.23</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46132</v>
+        <v>46171</v>
       </c>
       <c r="B159" t="s">
         <v>5</v>
       </c>
       <c r="C159">
-        <v>916.68</v>
+        <v>932.33</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46133</v>
+        <v>46172</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C160">
-        <v>982.07</v>
+        <v>1602.4</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46134</v>
+        <v>46172</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161">
-        <v>1110.42</v>
+        <v>960.49</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46135</v>
+        <v>46172</v>
       </c>
       <c r="B162" t="s">
         <v>5</v>
       </c>
       <c r="C162">
-        <v>1022.98</v>
+        <v>994.71</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46136</v>
+        <v>46173</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C163">
-        <v>1204.6300000000001</v>
+        <v>1425.5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46137</v>
+        <v>46173</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164">
-        <v>1144.56</v>
+        <v>930.07</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46138</v>
+        <v>46173</v>
       </c>
       <c r="B165" t="s">
         <v>5</v>
       </c>
       <c r="C165">
-        <v>990.51</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46139</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C166">
-        <v>754.98</v>
+        <v>853.4</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46140</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167">
-        <v>758.6</v>
+        <v>897.07</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="s">
         <v>5</v>
       </c>
       <c r="C168">
-        <v>759.8</v>
+        <v>767.55</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46142</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169">
-        <v>741.82</v>
+        <v>1158.77</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46143</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="s">
         <v>5</v>
       </c>
       <c r="C170">
-        <v>647.97</v>
+        <v>1034.02</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46144</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C171">
-        <v>811.24</v>
+        <v>576.04</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46145</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
-        <v>1538.71</v>
+        <v>1026.26</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46146</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="s">
         <v>5</v>
       </c>
       <c r="C173">
-        <v>1123.06</v>
+        <v>1324.51</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46147</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C174">
-        <v>1014.45</v>
+        <v>3125.43</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46148</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175">
-        <v>860.07</v>
+        <v>895.72</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46149</v>
+        <v>46177</v>
       </c>
       <c r="B176" t="s">
         <v>5</v>
       </c>
       <c r="C176">
-        <v>945.18</v>
+        <v>1059.71</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C177">
-        <v>1119.22</v>
+        <v>2189.2600000000002</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46151</v>
+        <v>46178</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178">
-        <v>1132.57</v>
+        <v>836.49</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46152</v>
+        <v>46178</v>
       </c>
       <c r="B179" t="s">
         <v>5</v>
       </c>
       <c r="C179">
-        <v>927.5</v>
+        <v>1076.56</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46153</v>
+        <v>46179</v>
       </c>
       <c r="B180" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C180">
-        <v>898.93</v>
+        <v>1761.01</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46154</v>
+        <v>46179</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181">
-        <v>903.1</v>
+        <v>1521.28</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46155</v>
+        <v>46179</v>
       </c>
       <c r="B182" t="s">
         <v>5</v>
       </c>
       <c r="C182">
-        <v>921.23</v>
+        <v>1095.47</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46156</v>
+        <v>46180</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C183">
-        <v>974.18</v>
+        <v>1829.97</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46157</v>
+        <v>46180</v>
       </c>
       <c r="B184" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184">
-        <v>1418.86</v>
+        <v>1212.58</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46158</v>
+        <v>46180</v>
       </c>
       <c r="B185" t="s">
         <v>5</v>
       </c>
       <c r="C185">
-        <v>978.18</v>
+        <v>1111.45</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46159</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C186">
-        <v>964.8</v>
+        <v>2359.3000000000002</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C187">
-        <v>911.14</v>
+        <v>981.26</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="s">
         <v>5</v>
       </c>
       <c r="C188">
-        <v>1006.19</v>
+        <v>863.95</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>46162</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C189">
-        <v>933.57</v>
+        <v>2694.6</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>46163</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C190">
-        <v>961.02</v>
+        <v>1002.08</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="B191" t="s">
         <v>5</v>
       </c>
       <c r="C191">
-        <v>983.94</v>
+        <v>1026.04</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
-        <v>46165</v>
+        <v>46183</v>
       </c>
       <c r="B192" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C192">
-        <v>960.65</v>
+        <v>298.89</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
-        <v>46166</v>
+        <v>46183</v>
       </c>
       <c r="B193" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C193">
-        <v>1083.08</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C194">
-        <v>884.8</v>
+        <v>997.2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
-        <v>46168</v>
+        <v>46183</v>
       </c>
       <c r="B195" t="s">
         <v>5</v>
       </c>
       <c r="C195">
-        <v>834.89</v>
+        <v>1100.55</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
-        <v>46169</v>
+        <v>46184</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C196">
-        <v>895.54</v>
+        <v>1690.68</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C197">
-        <v>924.29</v>
+        <v>822.2</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B198" t="s">
         <v>5</v>
       </c>
       <c r="C198">
-        <v>932.33</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
-        <v>46172</v>
+        <v>46185</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C199">
-        <v>994.71</v>
+        <v>911.1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
-        <v>46173</v>
+        <v>46185</v>
       </c>
       <c r="B200" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C200">
-        <v>915.54</v>
+        <v>669.78</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B201" t="s">
         <v>5</v>
       </c>
       <c r="C201">
-        <v>767.55</v>
+        <v>820.13</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
-        <v>46175</v>
+        <v>46186</v>
       </c>
       <c r="B202" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C202">
-        <v>1034.02</v>
+        <v>524.37</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
-        <v>46176</v>
+        <v>46186</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C203">
-        <v>1324.51</v>
+        <v>803.62</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
-        <v>46177</v>
+        <v>46186</v>
       </c>
       <c r="B204" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204">
-        <v>1059.71</v>
+        <v>1208.0999999999999</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
-        <v>46178</v>
+        <v>46186</v>
       </c>
       <c r="B205" t="s">
         <v>5</v>
       </c>
       <c r="C205">
-        <v>1076.56</v>
+        <v>1053.48</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
-        <v>46179</v>
+        <v>46187</v>
       </c>
       <c r="B206" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C206">
-        <v>1095.47</v>
+        <v>1197.73</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B207" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C207">
-        <v>1111.45</v>
+        <v>656.27</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
-        <v>46181</v>
+        <v>46187</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208">
-        <v>863.95</v>
+        <v>1582.98</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
-        <v>46182</v>
+        <v>46187</v>
       </c>
       <c r="B209" t="s">
         <v>5</v>
       </c>
       <c r="C209">
-        <v>1026.04</v>
+        <v>1377.55</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C210">
-        <v>1100.55</v>
+        <v>778.85</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C211">
-        <v>1007.25</v>
+        <v>679.73</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B212" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212">
-        <v>820.13</v>
+        <v>931.83</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B213" t="s">
         <v>5</v>
       </c>
       <c r="C213">
-        <v>1053.48</v>
+        <v>1001.64</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C214">
-        <v>1377.55</v>
+        <v>79.209999999999994</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B215" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C215">
-        <v>1001.64</v>
+        <v>617.65</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -2839,32 +2839,32 @@
         <v>46189</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C216">
-        <v>900.81</v>
+        <v>879.71</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C217">
-        <v>337.24</v>
+        <v>920.5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C218">
-        <v>491.46</v>
+        <v>900.81</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
@@ -2872,10 +2872,10 @@
         <v>46190</v>
       </c>
       <c r="B219" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C219">
-        <v>727.09</v>
+        <v>337.24</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
@@ -2883,10 +2883,10 @@
         <v>46190</v>
       </c>
       <c r="B220" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C220">
-        <v>918.2</v>
+        <v>491.46</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
@@ -2894,20 +2894,212 @@
         <v>46190</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C221">
+        <v>727.09</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+      <c r="C222">
+        <v>918.2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B223" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223">
         <v>959.32</v>
       </c>
     </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B224" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224">
+        <v>158.32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B225" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225">
+        <v>201.09</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B226" t="s">
+        <v>8</v>
+      </c>
+      <c r="C226">
+        <v>648.20000000000005</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227">
+        <v>838.96</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B228" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228">
+        <v>904.03</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B229" t="s">
+        <v>12</v>
+      </c>
+      <c r="C229">
+        <v>268.25</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B230" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230">
+        <v>171.75</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B231" t="s">
+        <v>8</v>
+      </c>
+      <c r="C231">
+        <v>1532.18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B232" t="s">
+        <v>4</v>
+      </c>
+      <c r="C232">
+        <v>1325.39</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B233" t="s">
+        <v>5</v>
+      </c>
+      <c r="C233">
+        <v>992.59</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234">
+        <v>199.26</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B235" t="s">
+        <v>13</v>
+      </c>
+      <c r="C235">
+        <v>156.12</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B236" t="s">
+        <v>8</v>
+      </c>
+      <c r="C236">
+        <v>1297.05</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B237" t="s">
+        <v>4</v>
+      </c>
+      <c r="C237">
+        <v>905.66</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B238" t="s">
+        <v>5</v>
+      </c>
+      <c r="C238">
+        <v>1175.95</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C238">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C208"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -2928,1933 +3120,2005 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>481.55</v>
+        <v>512.22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>3441.39</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>528.88</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
-        <v>459.4</v>
+        <v>484.39</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>3221.28</v>
+        <v>3180.49</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>478.65</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>497.39</v>
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>3276.72</v>
+        <v>3641.07</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>451.55</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>536.59</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>3486.04</v>
+        <v>3441.39</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13">
-        <v>493.55</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46186</v>
+        <v>46189</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>490.37</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46186</v>
+        <v>46189</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>2452.7199999999998</v>
+        <v>3221.28</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46186</v>
+        <v>46189</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>547.78</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>456.13</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>3072.14</v>
+        <v>3276.72</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>461.99</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>506.52</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2">
-        <v>3183.11</v>
+        <v>3486.04</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>506.99</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46183</v>
+        <v>46186</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>493.44</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46183</v>
+        <v>46186</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2">
-        <v>2587.6</v>
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46183</v>
+        <v>46186</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>458.08</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26">
-        <v>506.82</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>3838.27</v>
+        <v>3072.14</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>478.44</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29">
-        <v>492.98</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <v>2990.38</v>
+        <v>3183.11</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>512.85</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>551.54</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <v>1448.25</v>
+        <v>2587.6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>533.17999999999995</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>496.91</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>1318.78</v>
+        <v>3838.27</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>492.79</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>493.28</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <v>1276.5</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>467.42</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41">
-        <v>505.85</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <v>1257.7</v>
+        <v>1448.25</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>509.16</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>468.33</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <v>1267.75</v>
+        <v>1318.78</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>462.92</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47">
-        <v>500.73</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <v>1284.17</v>
+        <v>1276.5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B49" t="s">
         <v>6</v>
       </c>
       <c r="C49">
-        <v>521.47</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
       </c>
       <c r="C50">
-        <v>504.72</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="2">
-        <v>1359.4</v>
+        <v>1257.7</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>516.37</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
       <c r="C53">
-        <v>529.03</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="2">
-        <v>1335.7</v>
+        <v>1267.75</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>528.64</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56">
-        <v>502.21</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57" s="2">
-        <v>1322.84</v>
+        <v>1284.17</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>509.86</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59">
-        <v>508.81</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="2">
-        <v>1254.29</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>500.59</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62">
-        <v>514.72</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2">
-        <v>1248.17</v>
+        <v>1335.7</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>499.91</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
       </c>
       <c r="C65">
-        <v>539.37</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="2">
-        <v>1136.27</v>
+        <v>1322.84</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>505.09</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68">
-        <v>523.91999999999996</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
       <c r="C69" s="2">
-        <v>1173.17</v>
+        <v>1254.29</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>507.95</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71">
-        <v>429.65</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
-      <c r="C72">
-        <v>720.79</v>
+      <c r="C72" s="2">
+        <v>1248.17</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>451.19</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74">
-        <v>479.73</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
-      <c r="C75">
-        <v>705.94</v>
+      <c r="C75" s="2">
+        <v>1136.27</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>524.41999999999996</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
       </c>
       <c r="C77">
-        <v>509.26</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
-      <c r="C78">
-        <v>663.05</v>
+      <c r="C78" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>439.45</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
       </c>
       <c r="C80">
-        <v>446.07</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
       <c r="C81">
-        <v>692.07</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82">
-        <v>447.4</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83">
-        <v>403.4</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
       <c r="C84">
-        <v>669.52</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>466.82</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86">
-        <v>486.91</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
       <c r="C87">
-        <v>659.67</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>471.71</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B89" t="s">
         <v>7</v>
       </c>
       <c r="C89">
-        <v>532.58000000000004</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
       </c>
       <c r="C90">
-        <v>703.37</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>562.97</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B92" t="s">
         <v>7</v>
       </c>
       <c r="C92">
-        <v>505.15</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>668.52</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>506.5</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B95" t="s">
         <v>7</v>
       </c>
       <c r="C95">
-        <v>571.26</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>570.80999999999995</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>582.09</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B98" t="s">
         <v>7</v>
       </c>
       <c r="C98">
-        <v>449.56</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>420.48</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>454.06</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B101" t="s">
         <v>7</v>
       </c>
       <c r="C101">
-        <v>505.54</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>493.46</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>487.21</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>579.72</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>570.92999999999995</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B106" t="s">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>591.13</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
-        <v>531.26</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>547.42999999999995</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
       </c>
       <c r="C109">
-        <v>537.16999999999996</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>512.42999999999995</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>516.32000000000005</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>506.59</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>480.14</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114">
-        <v>477.63</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>451.42</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>440.24</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>473.37</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
       </c>
       <c r="C118">
-        <v>471.83</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>413.27</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>457.2</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>399.36</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>576.4</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123">
-        <v>458.96</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
       </c>
       <c r="C124">
-        <v>429.68</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>469.28</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B126" t="s">
         <v>3</v>
       </c>
       <c r="C126">
-        <v>462.4</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>446.33</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128">
-        <v>514.92999999999995</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>524.33000000000004</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>492.66</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131">
-        <v>525.04</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>555.08000000000004</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B133" t="s">
         <v>6</v>
       </c>
       <c r="C133">
-        <v>516.41999999999996</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134">
-        <v>529.30999999999995</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>544.63</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
       </c>
       <c r="C136">
-        <v>646.28</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137">
-        <v>467.75</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>496.42</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>566.66</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
       </c>
       <c r="C140">
-        <v>435.83</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141">
-        <v>468.24</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>507.5</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
       </c>
       <c r="C143">
-        <v>513.24</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
       </c>
       <c r="C144">
-        <v>442.08</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B145" t="s">
         <v>6</v>
       </c>
       <c r="C145">
-        <v>490.51</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
       </c>
       <c r="C146">
-        <v>455.23</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>390.46</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148">
-        <v>490.96</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149">
-        <v>416.64</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
       <c r="C150">
-        <v>473.63</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
       </c>
       <c r="C151">
-        <v>517.11</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
       </c>
       <c r="C152">
-        <v>481.26</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>633.22</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
       </c>
       <c r="C154">
-        <v>557.57000000000005</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155">
-        <v>595.71</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
       </c>
       <c r="C156">
-        <v>600.36</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>508.81</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
       </c>
       <c r="C158">
-        <v>598.64</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>490.83</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="s">
         <v>6</v>
       </c>
       <c r="C160">
-        <v>427.5</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161">
-        <v>270.85000000000002</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
       <c r="C162">
-        <v>333.98</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="B163" t="s">
         <v>6</v>
       </c>
       <c r="C163">
-        <v>184.94</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164">
-        <v>296.23</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>270.06</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B166" t="s">
         <v>6</v>
       </c>
       <c r="C166">
-        <v>284.88</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167">
-        <v>336.5</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>606.85</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="B169" t="s">
         <v>6</v>
       </c>
       <c r="C169">
-        <v>713.78</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170">
-        <v>766.34</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>536.29</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B172" t="s">
         <v>6</v>
       </c>
       <c r="C172">
-        <v>509.61</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173">
-        <v>750.08</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B174" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174">
+        <v>270.06</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B175" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175">
+        <v>284.88</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176">
+        <v>336.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B177" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177">
+        <v>606.85</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B178" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178">
+        <v>713.78</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179">
+        <v>766.34</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B180" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B181" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B182" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="1">
         <v>46132</v>
       </c>
-      <c r="B174" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174">
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="2">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="1"/>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="1"/>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="1"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" s="1"/>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="1"/>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" s="1"/>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="1"/>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="1"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="1"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1"/>
@@ -4914,7 +5178,6 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="1"/>
-      <c r="C201" s="2"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
@@ -4928,17 +5191,8 @@
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="1"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="1"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="1"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C174" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
+  <autoFilter ref="A1:C171" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4A40DD-D613-4159-B18A-1C0B003F29DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3227127E-B716-4B34-BEE4-CB9FA29BDD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="15">
   <si>
     <t>Day</t>
   </si>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C238"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3087,12 +3087,117 @@
         <v>1175.95</v>
       </c>
     </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B239" t="s">
+        <v>12</v>
+      </c>
+      <c r="C239">
+        <v>200.09</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B240" t="s">
+        <v>13</v>
+      </c>
+      <c r="C240">
+        <v>340.18</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B241" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241">
+        <v>1169.33</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B242" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242">
+        <v>1355.75</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B243" t="s">
+        <v>5</v>
+      </c>
+      <c r="C243">
+        <v>1229.8599999999999</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B244" t="s">
+        <v>12</v>
+      </c>
+      <c r="C244">
+        <v>412.2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245">
+        <v>96.71</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B246" t="s">
+        <v>8</v>
+      </c>
+      <c r="C246">
+        <v>916.28</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B247" t="s">
+        <v>4</v>
+      </c>
+      <c r="C247">
+        <v>921.27</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B248" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248">
+        <v>959.67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C238">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3120,2025 +3225,2071 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>512.22</v>
+        <v>535.29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>2204</v>
+        <v>3932.93</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>481.71</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
-        <v>484.39</v>
+        <v>544.71</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>3180.49</v>
+        <v>3551.97</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>486.4</v>
+        <v>540.75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>527.33000000000004</v>
+        <v>512.22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>3641.07</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>578.59</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>481.55</v>
+        <v>484.39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>3441.39</v>
+        <v>3180.49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13">
-        <v>528.88</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>459.4</v>
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>3221.28</v>
+        <v>3641.07</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>478.65</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>497.39</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>3276.72</v>
+        <v>3441.39</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>451.55</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>536.59</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2">
-        <v>3486.04</v>
+        <v>3221.28</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>493.55</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>490.37</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2">
-        <v>2452.7199999999998</v>
+        <v>3276.72</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>547.78</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26">
-        <v>456.13</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>3072.14</v>
+        <v>3486.04</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>461.99</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29">
-        <v>506.52</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <v>3183.11</v>
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>506.99</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>493.44</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <v>2587.6</v>
+        <v>3072.14</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>458.08</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>506.82</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>3838.27</v>
+        <v>3183.11</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>478.44</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>492.98</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <v>2990.38</v>
+        <v>2587.6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>512.85</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41">
-        <v>551.54</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <v>1448.25</v>
+        <v>3838.27</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>533.17999999999995</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>496.91</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <v>1318.78</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>492.79</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47">
-        <v>493.28</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <v>1276.5</v>
+        <v>1448.25</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B49" t="s">
         <v>6</v>
       </c>
       <c r="C49">
-        <v>467.42</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
       </c>
       <c r="C50">
-        <v>505.85</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="2">
-        <v>1257.7</v>
+        <v>1318.78</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>509.16</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
       <c r="C53">
-        <v>468.33</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="2">
-        <v>1267.75</v>
+        <v>1276.5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>462.92</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56">
-        <v>500.73</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57" s="2">
-        <v>1284.17</v>
+        <v>1257.7</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>521.47</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59">
-        <v>504.72</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="2">
-        <v>1359.4</v>
+        <v>1267.75</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>516.37</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62">
-        <v>529.03</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2">
-        <v>1335.7</v>
+        <v>1284.17</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>528.64</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
       </c>
       <c r="C65">
-        <v>502.21</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="2">
-        <v>1322.84</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>509.86</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68">
-        <v>508.81</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
       <c r="C69" s="2">
-        <v>1254.29</v>
+        <v>1335.7</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>500.59</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71">
-        <v>514.72</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
       <c r="C72" s="2">
-        <v>1248.17</v>
+        <v>1322.84</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>499.91</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74">
-        <v>539.37</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
       <c r="C75" s="2">
-        <v>1136.27</v>
+        <v>1254.29</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>505.09</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
       </c>
       <c r="C77">
-        <v>523.91999999999996</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="2">
-        <v>1173.17</v>
+        <v>1248.17</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>507.95</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
       </c>
       <c r="C80">
-        <v>429.65</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
-      <c r="C81">
-        <v>720.79</v>
+      <c r="C81" s="2">
+        <v>1136.27</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82">
-        <v>451.19</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83">
-        <v>479.73</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
-      <c r="C84">
-        <v>705.94</v>
+      <c r="C84" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>524.41999999999996</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86">
-        <v>509.26</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
       <c r="C87">
-        <v>663.05</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>439.45</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B89" t="s">
         <v>7</v>
       </c>
       <c r="C89">
-        <v>446.07</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
       </c>
       <c r="C90">
-        <v>692.07</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>447.4</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="B92" t="s">
         <v>7</v>
       </c>
       <c r="C92">
-        <v>403.4</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>669.52</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>466.82</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B95" t="s">
         <v>7</v>
       </c>
       <c r="C95">
-        <v>486.91</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>659.67</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>471.71</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B98" t="s">
         <v>7</v>
       </c>
       <c r="C98">
-        <v>532.58000000000004</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>703.37</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>562.97</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B101" t="s">
         <v>7</v>
       </c>
       <c r="C101">
-        <v>505.15</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>668.52</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>506.5</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>571.26</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>570.80999999999995</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B106" t="s">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>582.09</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
-        <v>449.56</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>420.48</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
       </c>
       <c r="C109">
-        <v>454.06</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>505.54</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>493.46</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>487.21</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>579.72</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114">
-        <v>570.92999999999995</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>591.13</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>531.26</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>547.42999999999995</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
       </c>
       <c r="C118">
-        <v>537.16999999999996</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>512.42999999999995</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>516.32000000000005</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>506.59</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>480.14</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123">
-        <v>477.63</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
       </c>
       <c r="C124">
-        <v>451.42</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>440.24</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B126" t="s">
         <v>3</v>
       </c>
       <c r="C126">
-        <v>473.37</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>471.83</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128">
-        <v>413.27</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>457.2</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>399.36</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131">
-        <v>576.4</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>458.96</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B133" t="s">
         <v>6</v>
       </c>
       <c r="C133">
-        <v>429.68</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134">
-        <v>469.28</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>462.4</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
       </c>
       <c r="C136">
-        <v>446.33</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137">
-        <v>514.92999999999995</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>524.33000000000004</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>492.66</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
       </c>
       <c r="C140">
-        <v>525.04</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141">
-        <v>555.08000000000004</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>516.41999999999996</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
       </c>
       <c r="C143">
-        <v>529.30999999999995</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
       </c>
       <c r="C144">
-        <v>544.63</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B145" t="s">
         <v>6</v>
       </c>
       <c r="C145">
-        <v>646.28</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
       </c>
       <c r="C146">
-        <v>467.75</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>496.42</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148">
-        <v>566.66</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149">
-        <v>435.83</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
       <c r="C150">
-        <v>468.24</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
       </c>
       <c r="C151">
-        <v>507.5</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
       </c>
       <c r="C152">
-        <v>513.24</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>442.08</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
       </c>
       <c r="C154">
-        <v>490.51</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155">
-        <v>455.23</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
       </c>
       <c r="C156">
-        <v>390.46</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>490.96</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
       </c>
       <c r="C158">
-        <v>416.64</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>473.63</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="s">
         <v>6</v>
       </c>
       <c r="C160">
-        <v>517.11</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161">
-        <v>481.26</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
       <c r="C162">
-        <v>633.22</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="s">
         <v>6</v>
       </c>
       <c r="C163">
-        <v>557.57000000000005</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164">
-        <v>595.71</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>600.36</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B166" t="s">
         <v>6</v>
       </c>
       <c r="C166">
-        <v>508.81</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167">
-        <v>598.64</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>490.83</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B169" t="s">
         <v>6</v>
       </c>
       <c r="C169">
-        <v>427.5</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170">
-        <v>270.85000000000002</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>333.98</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B172" t="s">
         <v>6</v>
       </c>
       <c r="C172">
-        <v>184.94</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173">
-        <v>296.23</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B174" t="s">
         <v>3</v>
       </c>
       <c r="C174">
-        <v>270.06</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B175" t="s">
         <v>6</v>
       </c>
       <c r="C175">
-        <v>284.88</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176">
-        <v>336.5</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B177" t="s">
         <v>3</v>
       </c>
       <c r="C177">
-        <v>606.85</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B178" t="s">
         <v>6</v>
       </c>
       <c r="C178">
-        <v>713.78</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179">
-        <v>766.34</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B180" t="s">
         <v>3</v>
       </c>
       <c r="C180">
-        <v>536.29</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B181" t="s">
         <v>6</v>
       </c>
       <c r="C181">
-        <v>509.61</v>
+        <v>284.88</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182">
-        <v>750.08</v>
+        <v>336.5</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B183" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="2">
+        <v>606.85</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B184" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184">
+        <v>713.78</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B185" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185">
+        <v>766.34</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B186" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="2">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B187" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="1">
         <v>46132</v>
       </c>
-      <c r="B183" t="s">
-        <v>7</v>
-      </c>
-      <c r="C183" s="2">
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="2">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" s="1"/>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" s="1"/>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" s="1"/>
-      <c r="C186" s="2"/>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" s="1"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" s="1"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" s="1"/>
-      <c r="C189" s="2"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3227127E-B716-4B34-BEE4-CB9FA29BDD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D8FB2-23D8-43D4-BBA5-52B180EEB78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="15">
   <si>
     <t>Day</t>
   </si>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C252"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3195,6 +3195,50 @@
       </c>
       <c r="C248">
         <v>959.67</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B249" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249">
+        <v>702.2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B250" t="s">
+        <v>8</v>
+      </c>
+      <c r="C250">
+        <v>701.85</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B251" t="s">
+        <v>4</v>
+      </c>
+      <c r="C251">
+        <v>918.89</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B252" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252">
+        <v>965.11</v>
       </c>
     </row>
   </sheetData>
@@ -3225,2081 +3269,2104 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>535.29</v>
+        <v>569.6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>3932.93</v>
+        <v>3907.64</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>548</v>
+        <v>571.69000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
-        <v>544.71</v>
+        <v>536.23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>3551.97</v>
+        <v>3945.77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>540.75</v>
+        <v>550.80999999999995</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>512.22</v>
+        <v>544.71</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>2204</v>
+        <v>3552.22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>481.71</v>
+        <v>540.75</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>484.39</v>
+        <v>512.22</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>3180.49</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13">
-        <v>486.4</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>527.33000000000004</v>
+        <v>484.39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>3641.07</v>
+        <v>3180.49</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>578.59</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>481.55</v>
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>3441.39</v>
+        <v>3641.07</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>528.88</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>459.4</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2">
-        <v>3221.28</v>
+        <v>3441.39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>478.65</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>497.39</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2">
-        <v>3276.72</v>
+        <v>3221.28</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>451.55</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26">
-        <v>536.59</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>3486.04</v>
+        <v>3276.72</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>493.55</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29">
-        <v>490.37</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <v>2452.7199999999998</v>
+        <v>3486.04</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>547.78</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>456.13</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <v>3072.14</v>
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>461.99</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>506.52</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>3183.11</v>
+        <v>3072.14</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>506.99</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>493.44</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <v>2587.6</v>
+        <v>3183.11</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>458.08</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41">
-        <v>506.82</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <v>3838.27</v>
+        <v>2587.6</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>478.44</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>492.98</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <v>2990.38</v>
+        <v>3838.27</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>512.85</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47">
-        <v>551.54</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <v>1448.25</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B49" t="s">
         <v>6</v>
       </c>
       <c r="C49">
-        <v>533.17999999999995</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
       </c>
       <c r="C50">
-        <v>496.91</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="2">
-        <v>1318.78</v>
+        <v>1448.25</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>492.79</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
       <c r="C53">
-        <v>493.28</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="2">
-        <v>1276.5</v>
+        <v>1318.78</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>467.42</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56">
-        <v>505.85</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57" s="2">
-        <v>1257.7</v>
+        <v>1276.5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>509.16</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59">
-        <v>468.33</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="2">
-        <v>1267.75</v>
+        <v>1257.7</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>462.92</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62">
-        <v>500.73</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2">
-        <v>1284.17</v>
+        <v>1267.75</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>521.47</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
       </c>
       <c r="C65">
-        <v>504.72</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="2">
-        <v>1359.4</v>
+        <v>1284.17</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>516.37</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68">
-        <v>529.03</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
       <c r="C69" s="2">
-        <v>1335.7</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>528.64</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71">
-        <v>502.21</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
       <c r="C72" s="2">
-        <v>1322.84</v>
+        <v>1335.7</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>509.86</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74">
-        <v>508.81</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
       <c r="C75" s="2">
-        <v>1254.29</v>
+        <v>1322.84</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>500.59</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
       </c>
       <c r="C77">
-        <v>514.72</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="2">
-        <v>1248.17</v>
+        <v>1254.29</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>499.91</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
       </c>
       <c r="C80">
-        <v>539.37</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="2">
-        <v>1136.27</v>
+        <v>1248.17</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82">
-        <v>505.09</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83">
-        <v>523.91999999999996</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
       <c r="C84" s="2">
-        <v>1173.17</v>
+        <v>1136.27</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>507.95</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86">
-        <v>429.65</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
-      <c r="C87">
-        <v>720.79</v>
+      <c r="C87" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>451.19</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B89" t="s">
         <v>7</v>
       </c>
       <c r="C89">
-        <v>479.73</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
       </c>
       <c r="C90">
-        <v>705.94</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>524.41999999999996</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B92" t="s">
         <v>7</v>
       </c>
       <c r="C92">
-        <v>509.26</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>663.05</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>439.45</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B95" t="s">
         <v>7</v>
       </c>
       <c r="C95">
-        <v>446.07</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>692.07</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>447.4</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98" t="s">
         <v>7</v>
       </c>
       <c r="C98">
-        <v>403.4</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>669.52</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>466.82</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B101" t="s">
         <v>7</v>
       </c>
       <c r="C101">
-        <v>486.91</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>659.67</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>471.71</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>532.58000000000004</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>703.37</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B106" t="s">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>562.97</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
-        <v>505.15</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>668.52</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
       </c>
       <c r="C109">
-        <v>506.5</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>571.26</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>570.80999999999995</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>582.09</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>449.56</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114">
-        <v>420.48</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>454.06</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>505.54</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>493.46</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
       </c>
       <c r="C118">
-        <v>487.21</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>579.72</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>570.92999999999995</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>591.13</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>531.26</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123">
-        <v>547.42999999999995</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
       </c>
       <c r="C124">
-        <v>537.16999999999996</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>512.42999999999995</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B126" t="s">
         <v>3</v>
       </c>
       <c r="C126">
-        <v>516.32000000000005</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>506.59</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128">
-        <v>480.14</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>477.63</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>451.42</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131">
-        <v>440.24</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>473.37</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B133" t="s">
         <v>6</v>
       </c>
       <c r="C133">
-        <v>471.83</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134">
-        <v>413.27</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>457.2</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
       </c>
       <c r="C136">
-        <v>399.36</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137">
-        <v>576.4</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>458.96</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>429.68</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
       </c>
       <c r="C140">
-        <v>469.28</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141">
-        <v>462.4</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>446.33</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
       </c>
       <c r="C143">
-        <v>514.92999999999995</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
       </c>
       <c r="C144">
-        <v>524.33000000000004</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B145" t="s">
         <v>6</v>
       </c>
       <c r="C145">
-        <v>492.66</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
       </c>
       <c r="C146">
-        <v>525.04</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>555.08000000000004</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148">
-        <v>516.41999999999996</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149">
-        <v>529.30999999999995</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
       <c r="C150">
-        <v>544.63</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
       </c>
       <c r="C151">
-        <v>646.28</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
       </c>
       <c r="C152">
-        <v>467.75</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>496.42</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
       </c>
       <c r="C154">
-        <v>566.66</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155">
-        <v>435.83</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
       </c>
       <c r="C156">
-        <v>468.24</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>507.5</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
       </c>
       <c r="C158">
-        <v>513.24</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>442.08</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B160" t="s">
         <v>6</v>
       </c>
       <c r="C160">
-        <v>490.51</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161">
-        <v>455.23</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
       <c r="C162">
-        <v>390.46</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="s">
         <v>6</v>
       </c>
       <c r="C163">
-        <v>490.96</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164">
-        <v>416.64</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>473.63</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B166" t="s">
         <v>6</v>
       </c>
       <c r="C166">
-        <v>517.11</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167">
-        <v>481.26</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>633.22</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B169" t="s">
         <v>6</v>
       </c>
       <c r="C169">
-        <v>557.57000000000005</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170">
-        <v>595.71</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>600.36</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B172" t="s">
         <v>6</v>
       </c>
       <c r="C172">
-        <v>508.81</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173">
-        <v>598.64</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B174" t="s">
         <v>3</v>
       </c>
       <c r="C174">
-        <v>490.83</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B175" t="s">
         <v>6</v>
       </c>
       <c r="C175">
-        <v>427.5</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176">
-        <v>270.85000000000002</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B177" t="s">
         <v>3</v>
       </c>
       <c r="C177">
-        <v>333.98</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B178" t="s">
         <v>6</v>
       </c>
       <c r="C178">
-        <v>184.94</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179">
-        <v>296.23</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B180" t="s">
         <v>3</v>
       </c>
       <c r="C180">
-        <v>270.06</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B181" t="s">
         <v>6</v>
       </c>
       <c r="C181">
-        <v>284.88</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182">
-        <v>336.5</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B183" t="s">
         <v>3</v>
       </c>
       <c r="C183" s="2">
-        <v>606.85</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B184" t="s">
         <v>6</v>
       </c>
       <c r="C184">
-        <v>713.78</v>
+        <v>284.88</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185">
-        <v>766.34</v>
+        <v>336.5</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B186" t="s">
         <v>3</v>
       </c>
       <c r="C186" s="2">
-        <v>536.29</v>
+        <v>606.85</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B187" t="s">
         <v>6</v>
       </c>
       <c r="C187">
-        <v>509.61</v>
+        <v>713.78</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
       </c>
       <c r="C188">
-        <v>750.08</v>
+        <v>766.34</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B189" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="2">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B190" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B191" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="1">
         <v>46132</v>
       </c>
-      <c r="B189" t="s">
-        <v>7</v>
-      </c>
-      <c r="C189" s="2">
+      <c r="B192" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="2">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" s="1"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" s="1"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" s="1"/>
-      <c r="C192" s="2"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D8FB2-23D8-43D4-BBA5-52B180EEB78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F23886-CC8A-4ADF-9B62-D0E7F3F57483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="15">
   <si>
     <t>Day</t>
   </si>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C256"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3239,6 +3239,50 @@
       </c>
       <c r="C252">
         <v>965.11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B253" t="s">
+        <v>12</v>
+      </c>
+      <c r="C253">
+        <v>656.76</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B254" t="s">
+        <v>8</v>
+      </c>
+      <c r="C254">
+        <v>700.79</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B255" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255">
+        <v>911.98</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B256" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256">
+        <v>953.49</v>
       </c>
     </row>
   </sheetData>
@@ -3269,2114 +3313,2137 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>569.6</v>
+        <v>692.77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>3907.64</v>
+        <v>3665.23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4">
-        <v>571.69000000000005</v>
+        <v>683.88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
-        <v>536.23</v>
+        <v>571.57000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>3945.77</v>
+        <v>3915.06</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>550.80999999999995</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>544.71</v>
+        <v>536.23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>3552.22</v>
+        <v>3945.97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10">
-        <v>540.75</v>
+        <v>550.80999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>512.22</v>
+        <v>544.71</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>2204</v>
+        <v>3552.22</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13">
-        <v>481.71</v>
+        <v>540.75</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>484.39</v>
+        <v>512.22</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>3180.49</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>486.4</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>527.33000000000004</v>
+        <v>484.39</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>3641.07</v>
+        <v>3180.49</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>578.59</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>481.55</v>
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2">
-        <v>3441.39</v>
+        <v>3641.07</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>528.88</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>459.4</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2">
-        <v>3221.28</v>
+        <v>3441.39</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>478.65</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26">
-        <v>497.39</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>3276.72</v>
+        <v>3221.28</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>451.55</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29">
-        <v>536.59</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="2">
-        <v>3486.04</v>
+        <v>3276.72</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>493.55</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>490.37</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2">
-        <v>2452.7199999999998</v>
+        <v>3486.04</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>547.78</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>456.13</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="2">
-        <v>3072.14</v>
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>461.99</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>506.52</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2">
-        <v>3183.11</v>
+        <v>3072.14</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>506.99</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41">
-        <v>493.44</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="2">
-        <v>2587.6</v>
+        <v>3183.11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>458.08</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>506.82</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="2">
-        <v>3838.27</v>
+        <v>2587.6</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>478.44</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47">
-        <v>492.98</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="2">
-        <v>2990.38</v>
+        <v>3838.27</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B49" t="s">
         <v>6</v>
       </c>
       <c r="C49">
-        <v>512.85</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
       </c>
       <c r="C50">
-        <v>551.54</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="2">
-        <v>1448.25</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>533.17999999999995</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
       <c r="C53">
-        <v>496.91</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="2">
-        <v>1318.78</v>
+        <v>1448.25</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>492.79</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56">
-        <v>493.28</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57" s="2">
-        <v>1276.5</v>
+        <v>1318.78</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>467.42</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59">
-        <v>505.85</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="2">
-        <v>1257.7</v>
+        <v>1276.5</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>509.16</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62">
-        <v>468.33</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2">
-        <v>1267.75</v>
+        <v>1257.7</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>462.92</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
       </c>
       <c r="C65">
-        <v>500.73</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
       <c r="C66" s="2">
-        <v>1284.17</v>
+        <v>1267.75</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>521.47</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68">
-        <v>504.72</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
       <c r="C69" s="2">
-        <v>1359.4</v>
+        <v>1284.17</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>516.37</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71">
-        <v>529.03</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
       <c r="C72" s="2">
-        <v>1335.7</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>528.64</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74">
-        <v>502.21</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
       <c r="C75" s="2">
-        <v>1322.84</v>
+        <v>1335.7</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>509.86</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
       </c>
       <c r="C77">
-        <v>508.81</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="2">
-        <v>1254.29</v>
+        <v>1322.84</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>500.59</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
       </c>
       <c r="C80">
-        <v>514.72</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="2">
-        <v>1248.17</v>
+        <v>1254.29</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82">
-        <v>499.91</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83">
-        <v>539.37</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
       <c r="C84" s="2">
-        <v>1136.27</v>
+        <v>1248.17</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>505.09</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86">
-        <v>523.91999999999996</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
       <c r="C87" s="2">
-        <v>1173.17</v>
+        <v>1136.27</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>507.95</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B89" t="s">
         <v>7</v>
       </c>
       <c r="C89">
-        <v>429.65</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
       </c>
-      <c r="C90">
-        <v>720.79</v>
+      <c r="C90" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>451.19</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B92" t="s">
         <v>7</v>
       </c>
       <c r="C92">
-        <v>479.73</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>705.94</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>524.41999999999996</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B95" t="s">
         <v>7</v>
       </c>
       <c r="C95">
-        <v>509.26</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>663.05</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>439.45</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98" t="s">
         <v>7</v>
       </c>
       <c r="C98">
-        <v>446.07</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>692.07</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>447.4</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B101" t="s">
         <v>7</v>
       </c>
       <c r="C101">
-        <v>403.4</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>669.52</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>466.82</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>486.91</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
       <c r="C105">
-        <v>659.67</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B106" t="s">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>471.71</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
-        <v>532.58000000000004</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>703.37</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
       </c>
       <c r="C109">
-        <v>562.97</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>505.15</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
       </c>
       <c r="C111">
-        <v>668.52</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B112" t="s">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>506.5</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>571.26</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114">
-        <v>570.80999999999995</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>582.09</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>449.56</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>420.48</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
       </c>
       <c r="C118">
-        <v>454.06</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>505.54</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
       </c>
       <c r="C120">
-        <v>493.46</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>487.21</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>579.72</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123">
-        <v>570.92999999999995</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
       </c>
       <c r="C124">
-        <v>591.13</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>531.26</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B126" t="s">
         <v>3</v>
       </c>
       <c r="C126">
-        <v>547.42999999999995</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>537.16999999999996</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128">
-        <v>512.42999999999995</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>516.32000000000005</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>506.59</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
       </c>
       <c r="C131">
-        <v>480.14</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>477.63</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B133" t="s">
         <v>6</v>
       </c>
       <c r="C133">
-        <v>451.42</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
       </c>
       <c r="C134">
-        <v>440.24</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>473.37</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
       </c>
       <c r="C136">
-        <v>471.83</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
       </c>
       <c r="C137">
-        <v>413.27</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>457.2</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B139" t="s">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>399.36</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
       </c>
       <c r="C140">
-        <v>576.4</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141">
-        <v>458.96</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B142" t="s">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>429.68</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
       </c>
       <c r="C143">
-        <v>469.28</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
       </c>
       <c r="C144">
-        <v>462.4</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B145" t="s">
         <v>6</v>
       </c>
       <c r="C145">
-        <v>446.33</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
       </c>
       <c r="C146">
-        <v>514.92999999999995</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>524.33000000000004</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148">
-        <v>492.66</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149">
-        <v>525.04</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
       </c>
       <c r="C150">
-        <v>555.08000000000004</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
       </c>
       <c r="C151">
-        <v>516.41999999999996</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
       </c>
       <c r="C152">
-        <v>529.30999999999995</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>544.63</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
       </c>
       <c r="C154">
-        <v>646.28</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155">
-        <v>467.75</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
       </c>
       <c r="C156">
-        <v>496.42</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
       </c>
       <c r="C157">
-        <v>566.66</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
       </c>
       <c r="C158">
-        <v>435.83</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>468.24</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B160" t="s">
         <v>6</v>
       </c>
       <c r="C160">
-        <v>507.5</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B161" t="s">
         <v>7</v>
       </c>
       <c r="C161">
-        <v>513.24</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
       <c r="C162">
-        <v>442.08</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B163" t="s">
         <v>6</v>
       </c>
       <c r="C163">
-        <v>490.51</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164">
-        <v>455.23</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
       <c r="C165">
-        <v>390.46</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B166" t="s">
         <v>6</v>
       </c>
       <c r="C166">
-        <v>490.96</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B167" t="s">
         <v>7</v>
       </c>
       <c r="C167">
-        <v>416.64</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
       </c>
       <c r="C168">
-        <v>473.63</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B169" t="s">
         <v>6</v>
       </c>
       <c r="C169">
-        <v>517.11</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170">
-        <v>481.26</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>633.22</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B172" t="s">
         <v>6</v>
       </c>
       <c r="C172">
-        <v>557.57000000000005</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
       </c>
       <c r="C173">
-        <v>595.71</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B174" t="s">
         <v>3</v>
       </c>
       <c r="C174">
-        <v>600.36</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B175" t="s">
         <v>6</v>
       </c>
       <c r="C175">
-        <v>508.81</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B176" t="s">
         <v>7</v>
       </c>
       <c r="C176">
-        <v>598.64</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B177" t="s">
         <v>3</v>
       </c>
       <c r="C177">
-        <v>490.83</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B178" t="s">
         <v>6</v>
       </c>
       <c r="C178">
-        <v>427.5</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
       </c>
       <c r="C179">
-        <v>270.85000000000002</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B180" t="s">
         <v>3</v>
       </c>
       <c r="C180">
-        <v>333.98</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B181" t="s">
         <v>6</v>
       </c>
       <c r="C181">
-        <v>184.94</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182">
-        <v>296.23</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B183" t="s">
         <v>3</v>
       </c>
       <c r="C183" s="2">
-        <v>270.06</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B184" t="s">
         <v>6</v>
       </c>
       <c r="C184">
-        <v>284.88</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185">
-        <v>336.5</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B186" t="s">
         <v>3</v>
       </c>
       <c r="C186" s="2">
-        <v>606.85</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B187" t="s">
         <v>6</v>
       </c>
       <c r="C187">
-        <v>713.78</v>
+        <v>284.88</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
       </c>
       <c r="C188">
-        <v>766.34</v>
+        <v>336.5</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B189" t="s">
         <v>3</v>
       </c>
       <c r="C189" s="2">
-        <v>536.29</v>
+        <v>606.85</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B190" t="s">
         <v>6</v>
       </c>
       <c r="C190">
-        <v>509.61</v>
+        <v>713.78</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191">
-        <v>750.08</v>
+        <v>766.34</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B192" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="2">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B194" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="1">
         <v>46132</v>
       </c>
-      <c r="B192" t="s">
-        <v>7</v>
-      </c>
-      <c r="C192" s="2">
+      <c r="B195" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="2">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" s="1"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" s="1"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" s="1"/>
-      <c r="C195" s="2"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="1"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F23886-CC8A-4ADF-9B62-D0E7F3F57483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB11CB-F16C-455D-979F-358C3C5732AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$256</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB11CB-F16C-455D-979F-358C3C5732AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21A757-411B-4C2E-A515-401424D58AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>AHM-UCR-Catalogue-Ads</t>
   </si>
   <si>
-    <t>Nasik-Search-Buy-UsedCar-8april</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -89,6 +86,9 @@
   </si>
   <si>
     <t>Nashik-DSA-UsedCars-Discovery</t>
+  </si>
+  <si>
+    <t>Nashik-Search-Buy-UsedCar-8april</t>
   </si>
 </sst>
 </file>
@@ -507,7 +507,7 @@
         <v>46120</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>64.97</v>
@@ -540,7 +540,7 @@
         <v>46121</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>628.70000000000005</v>
@@ -573,7 +573,7 @@
         <v>46122</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>632.29</v>
@@ -606,7 +606,7 @@
         <v>46123</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>374.88</v>
@@ -639,7 +639,7 @@
         <v>46124</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>532.29999999999995</v>
@@ -672,7 +672,7 @@
         <v>46125</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C19">
         <v>620.17999999999995</v>
@@ -705,7 +705,7 @@
         <v>46126</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C22">
         <v>1437.37</v>
@@ -738,7 +738,7 @@
         <v>46127</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25">
         <v>1094.69</v>
@@ -771,7 +771,7 @@
         <v>46128</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C28">
         <v>911.37</v>
@@ -804,7 +804,7 @@
         <v>46129</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C31">
         <v>1061.49</v>
@@ -837,7 +837,7 @@
         <v>46130</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C34">
         <v>1085.51</v>
@@ -870,7 +870,7 @@
         <v>46131</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C37">
         <v>999.47</v>
@@ -903,7 +903,7 @@
         <v>46132</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C40">
         <v>975.32</v>
@@ -936,7 +936,7 @@
         <v>46133</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C43">
         <v>1047.22</v>
@@ -969,7 +969,7 @@
         <v>46134</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C46">
         <v>1259.8699999999999</v>
@@ -1002,7 +1002,7 @@
         <v>46135</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C49">
         <v>1064.55</v>
@@ -1035,7 +1035,7 @@
         <v>46136</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C52">
         <v>996.48</v>
@@ -1068,7 +1068,7 @@
         <v>46137</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C55">
         <v>1312.03</v>
@@ -1101,7 +1101,7 @@
         <v>46138</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C58">
         <v>1028.4100000000001</v>
@@ -1134,7 +1134,7 @@
         <v>46139</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C61">
         <v>788.39</v>
@@ -1167,7 +1167,7 @@
         <v>46140</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C64">
         <v>773.31</v>
@@ -1200,7 +1200,7 @@
         <v>46141</v>
       </c>
       <c r="B67" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C67">
         <v>773.36</v>
@@ -1233,7 +1233,7 @@
         <v>46142</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C70">
         <v>776.21</v>
@@ -1266,7 +1266,7 @@
         <v>46143</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C73">
         <v>896.44</v>
@@ -1299,7 +1299,7 @@
         <v>46144</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C76">
         <v>977.68</v>
@@ -1332,7 +1332,7 @@
         <v>46145</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C79">
         <v>1365.79</v>
@@ -1365,7 +1365,7 @@
         <v>46146</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C82">
         <v>883.13</v>
@@ -1398,7 +1398,7 @@
         <v>46147</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C85">
         <v>885.01</v>
@@ -1431,7 +1431,7 @@
         <v>46148</v>
       </c>
       <c r="B88" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C88">
         <v>771.48</v>
@@ -1464,7 +1464,7 @@
         <v>46149</v>
       </c>
       <c r="B91" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C91">
         <v>1129.58</v>
@@ -1497,7 +1497,7 @@
         <v>46150</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C94">
         <v>1237.75</v>
@@ -1530,7 +1530,7 @@
         <v>46151</v>
       </c>
       <c r="B97" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C97">
         <v>1036.03</v>
@@ -1563,7 +1563,7 @@
         <v>46152</v>
       </c>
       <c r="B100" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C100">
         <v>1041.58</v>
@@ -1596,7 +1596,7 @@
         <v>46153</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C103">
         <v>1050.2</v>
@@ -1629,7 +1629,7 @@
         <v>46154</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C106">
         <v>963.55</v>
@@ -1662,7 +1662,7 @@
         <v>46155</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C109">
         <v>852.6</v>
@@ -1695,7 +1695,7 @@
         <v>46156</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C112">
         <v>929.18</v>
@@ -1728,7 +1728,7 @@
         <v>46157</v>
       </c>
       <c r="B115" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C115">
         <v>1007.08</v>
@@ -1761,7 +1761,7 @@
         <v>46158</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C118">
         <v>1190.55</v>
@@ -1794,7 +1794,7 @@
         <v>46159</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C121">
         <v>1025.94</v>
@@ -1827,7 +1827,7 @@
         <v>46160</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C124">
         <v>883.7</v>
@@ -1860,7 +1860,7 @@
         <v>46161</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C127">
         <v>822.74</v>
@@ -1893,7 +1893,7 @@
         <v>46162</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C130">
         <v>889.78</v>
@@ -1926,7 +1926,7 @@
         <v>46163</v>
       </c>
       <c r="B133" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C133">
         <v>1238.71</v>
@@ -1959,7 +1959,7 @@
         <v>46164</v>
       </c>
       <c r="B136" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C136">
         <v>960.3</v>
@@ -1992,7 +1992,7 @@
         <v>46165</v>
       </c>
       <c r="B139" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C139">
         <v>1035.1300000000001</v>
@@ -2025,7 +2025,7 @@
         <v>46166</v>
       </c>
       <c r="B142" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C142">
         <v>935.29</v>
@@ -2058,7 +2058,7 @@
         <v>46167</v>
       </c>
       <c r="B145" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C145">
         <v>1300.27</v>
@@ -2091,7 +2091,7 @@
         <v>46168</v>
       </c>
       <c r="B148" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C148">
         <v>1691.22</v>
@@ -2124,7 +2124,7 @@
         <v>46169</v>
       </c>
       <c r="B151" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C151">
         <v>1719.87</v>
@@ -2157,7 +2157,7 @@
         <v>46170</v>
       </c>
       <c r="B154" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C154">
         <v>1581.56</v>
@@ -2190,7 +2190,7 @@
         <v>46171</v>
       </c>
       <c r="B157" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C157">
         <v>1577.46</v>
@@ -2223,7 +2223,7 @@
         <v>46172</v>
       </c>
       <c r="B160" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C160">
         <v>1602.4</v>
@@ -2256,7 +2256,7 @@
         <v>46173</v>
       </c>
       <c r="B163" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C163">
         <v>1425.5</v>
@@ -2289,7 +2289,7 @@
         <v>46174</v>
       </c>
       <c r="B166" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C166">
         <v>853.4</v>
@@ -2344,7 +2344,7 @@
         <v>46176</v>
       </c>
       <c r="B171" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C171">
         <v>576.04</v>
@@ -2377,7 +2377,7 @@
         <v>46177</v>
       </c>
       <c r="B174" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C174">
         <v>3125.43</v>
@@ -2410,7 +2410,7 @@
         <v>46178</v>
       </c>
       <c r="B177" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C177">
         <v>2189.2600000000002</v>
@@ -2443,7 +2443,7 @@
         <v>46179</v>
       </c>
       <c r="B180" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C180">
         <v>1761.01</v>
@@ -2476,7 +2476,7 @@
         <v>46180</v>
       </c>
       <c r="B183" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C183">
         <v>1829.97</v>
@@ -2509,7 +2509,7 @@
         <v>46181</v>
       </c>
       <c r="B186" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C186">
         <v>2359.3000000000002</v>
@@ -2542,7 +2542,7 @@
         <v>46182</v>
       </c>
       <c r="B189" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C189">
         <v>2694.6</v>
@@ -2575,7 +2575,7 @@
         <v>46183</v>
       </c>
       <c r="B192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C192">
         <v>298.89</v>
@@ -2586,7 +2586,7 @@
         <v>46183</v>
       </c>
       <c r="B193" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C193">
         <v>2818.5</v>
@@ -2619,7 +2619,7 @@
         <v>46184</v>
       </c>
       <c r="B196" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C196">
         <v>1690.68</v>
@@ -2652,7 +2652,7 @@
         <v>46185</v>
       </c>
       <c r="B199" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C199">
         <v>911.1</v>
@@ -2685,7 +2685,7 @@
         <v>46186</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C202">
         <v>524.37</v>
@@ -2696,7 +2696,7 @@
         <v>46186</v>
       </c>
       <c r="B203" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C203">
         <v>803.62</v>
@@ -2729,7 +2729,7 @@
         <v>46187</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C206">
         <v>1197.73</v>
@@ -2740,7 +2740,7 @@
         <v>46187</v>
       </c>
       <c r="B207" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C207">
         <v>656.27</v>
@@ -2773,7 +2773,7 @@
         <v>46188</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C210">
         <v>778.85</v>
@@ -2784,7 +2784,7 @@
         <v>46188</v>
       </c>
       <c r="B211" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C211">
         <v>679.73</v>
@@ -2817,7 +2817,7 @@
         <v>46189</v>
       </c>
       <c r="B214" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C214">
         <v>79.209999999999994</v>
@@ -2828,7 +2828,7 @@
         <v>46189</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C215">
         <v>617.65</v>
@@ -2839,7 +2839,7 @@
         <v>46189</v>
       </c>
       <c r="B216" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C216">
         <v>879.71</v>
@@ -2872,7 +2872,7 @@
         <v>46190</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C219">
         <v>337.24</v>
@@ -2883,7 +2883,7 @@
         <v>46190</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C220">
         <v>491.46</v>
@@ -2894,7 +2894,7 @@
         <v>46190</v>
       </c>
       <c r="B221" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C221">
         <v>727.09</v>
@@ -2927,7 +2927,7 @@
         <v>46191</v>
       </c>
       <c r="B224" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C224">
         <v>158.32</v>
@@ -2938,7 +2938,7 @@
         <v>46191</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C225">
         <v>201.09</v>
@@ -2949,7 +2949,7 @@
         <v>46191</v>
       </c>
       <c r="B226" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C226">
         <v>648.20000000000005</v>
@@ -2982,7 +2982,7 @@
         <v>46192</v>
       </c>
       <c r="B229" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C229">
         <v>268.25</v>
@@ -2993,7 +2993,7 @@
         <v>46192</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C230">
         <v>171.75</v>
@@ -3004,7 +3004,7 @@
         <v>46192</v>
       </c>
       <c r="B231" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C231">
         <v>1532.18</v>
@@ -3037,7 +3037,7 @@
         <v>46193</v>
       </c>
       <c r="B234" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C234">
         <v>199.26</v>
@@ -3048,7 +3048,7 @@
         <v>46193</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C235">
         <v>156.12</v>
@@ -3059,7 +3059,7 @@
         <v>46193</v>
       </c>
       <c r="B236" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C236">
         <v>1297.05</v>
@@ -3092,7 +3092,7 @@
         <v>46194</v>
       </c>
       <c r="B239" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C239">
         <v>200.09</v>
@@ -3103,7 +3103,7 @@
         <v>46194</v>
       </c>
       <c r="B240" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C240">
         <v>340.18</v>
@@ -3114,7 +3114,7 @@
         <v>46194</v>
       </c>
       <c r="B241" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C241">
         <v>1169.33</v>
@@ -3147,7 +3147,7 @@
         <v>46195</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C244">
         <v>412.2</v>
@@ -3158,7 +3158,7 @@
         <v>46195</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C245">
         <v>96.71</v>
@@ -3169,7 +3169,7 @@
         <v>46195</v>
       </c>
       <c r="B246" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C246">
         <v>916.28</v>
@@ -3202,7 +3202,7 @@
         <v>46196</v>
       </c>
       <c r="B249" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C249">
         <v>702.2</v>
@@ -3213,7 +3213,7 @@
         <v>46196</v>
       </c>
       <c r="B250" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C250">
         <v>701.85</v>
@@ -3246,7 +3246,7 @@
         <v>46197</v>
       </c>
       <c r="B253" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C253">
         <v>656.76</v>
@@ -3257,7 +3257,7 @@
         <v>46197</v>
       </c>
       <c r="B254" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C254">
         <v>700.79</v>
@@ -3302,13 +3302,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21A757-411B-4C2E-A515-401424D58AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701B9EF7-BDA3-4B29-9B5B-8DF30388537C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
     <sheet name="FB" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FB!$A$1:$C$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ga!$A$1:$C$256</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Nashik-Search-Buy-UsedCar-8april</t>
+  </si>
+  <si>
+    <t>Nasik-Search-Buy-UsedCar-8april</t>
+  </si>
+  <si>
+    <t>UCR-Lead-Luxury-Cart-Classified-Jan25</t>
   </si>
 </sst>
 </file>
@@ -462,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C260"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3285,6 +3291,50 @@
         <v>953.49</v>
       </c>
     </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257">
+        <v>638.82000000000005</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B258" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258">
+        <v>755.97</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B259" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259">
+        <v>1166.57</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260">
+        <v>1122.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3292,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C209"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -3313,2150 +3363,2181 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>692.77</v>
+        <v>401.76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3665.23</v>
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>955.81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>683.88</v>
+        <v>1846.72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>571.57000000000005</v>
+        <v>759.99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3915.06</v>
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>692.77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>573</v>
+        <v>3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3665.23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>536.23</v>
+        <v>683.88</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3945.97</v>
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>571.57000000000005</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>550.80999999999995</v>
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3915.06</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>544.71</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3552.22</v>
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>536.23</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>540.75</v>
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3945.97</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>512.22</v>
+        <v>550.80999999999995</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2204</v>
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>544.71</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>481.71</v>
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3552.22</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>484.39</v>
+        <v>540.75</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3180.49</v>
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>512.22</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19">
-        <v>486.4</v>
+        <v>3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2204</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>527.33000000000004</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3641.07</v>
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>484.39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22">
-        <v>578.59</v>
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3180.49</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>481.55</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3441.39</v>
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>528.88</v>
+        <v>3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3641.07</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>459.4</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3221.28</v>
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>481.55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28">
-        <v>478.65</v>
+        <v>3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3441.39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>497.39</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="2">
-        <v>3276.72</v>
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>459.4</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>451.55</v>
+        <v>3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>3221.28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>536.59</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="2">
-        <v>3486.04</v>
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>497.39</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34">
-        <v>493.55</v>
+        <v>3</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3276.72</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>490.37</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="2">
-        <v>2452.7199999999998</v>
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>536.59</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37">
-        <v>547.78</v>
+        <v>3</v>
+      </c>
+      <c r="C37" s="2">
+        <v>3486.04</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>456.13</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="2">
-        <v>3072.14</v>
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>490.37</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>461.99</v>
+        <v>3</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>506.52</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="2">
-        <v>3183.11</v>
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>456.13</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43">
-        <v>506.99</v>
+        <v>3</v>
+      </c>
+      <c r="C43" s="2">
+        <v>3072.14</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>493.44</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B45" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2587.6</v>
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>506.52</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
-        <v>458.08</v>
+        <v>3</v>
+      </c>
+      <c r="C46" s="2">
+        <v>3183.11</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>506.82</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="2">
-        <v>3838.27</v>
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>493.44</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49">
-        <v>478.44</v>
+        <v>3</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2587.6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50">
-        <v>492.98</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B51" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="2">
-        <v>2990.38</v>
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>506.82</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52">
-        <v>512.85</v>
+        <v>3</v>
+      </c>
+      <c r="C52" s="2">
+        <v>3838.27</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53">
-        <v>551.54</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1448.25</v>
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>492.98</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55">
-        <v>533.17999999999995</v>
+        <v>3</v>
+      </c>
+      <c r="C55" s="2">
+        <v>2990.38</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56">
-        <v>496.91</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1318.78</v>
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>551.54</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58">
-        <v>492.79</v>
+        <v>3</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1448.25</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59">
-        <v>493.28</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B60" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1276.5</v>
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>496.91</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61">
-        <v>467.42</v>
+        <v>3</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1318.78</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>505.85</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1257.7</v>
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>493.28</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64">
-        <v>509.16</v>
+        <v>3</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1276.5</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65">
-        <v>468.33</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B66" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="2">
-        <v>1267.75</v>
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>505.85</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67">
-        <v>462.92</v>
+        <v>3</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1257.7</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68">
-        <v>500.73</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B69" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="2">
-        <v>1284.17</v>
+        <v>7</v>
+      </c>
+      <c r="C69">
+        <v>468.33</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70">
-        <v>521.47</v>
+        <v>3</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1267.75</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>504.72</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B72" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1359.4</v>
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>500.73</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73">
-        <v>516.37</v>
+        <v>3</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1284.17</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74">
-        <v>529.03</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B75" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="2">
-        <v>1335.7</v>
+        <v>7</v>
+      </c>
+      <c r="C75">
+        <v>504.72</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76">
-        <v>528.64</v>
+        <v>3</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1359.4</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="B77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77">
-        <v>502.21</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" s="2">
-        <v>1322.84</v>
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>529.03</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79">
-        <v>509.86</v>
+        <v>3</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1335.7</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="B80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80">
-        <v>508.81</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B81" t="s">
-        <v>3</v>
-      </c>
-      <c r="C81" s="2">
-        <v>1254.29</v>
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>502.21</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82">
-        <v>500.59</v>
+        <v>3</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1322.84</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>514.72</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B84" t="s">
-        <v>3</v>
-      </c>
-      <c r="C84" s="2">
-        <v>1248.17</v>
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>508.81</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85">
-        <v>499.91</v>
+        <v>3</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1254.29</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86">
-        <v>539.37</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B87" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="2">
-        <v>1136.27</v>
+        <v>7</v>
+      </c>
+      <c r="C87">
+        <v>514.72</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88">
-        <v>505.09</v>
+        <v>3</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1248.17</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>523.91999999999996</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B90" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="2">
-        <v>1173.17</v>
+        <v>7</v>
+      </c>
+      <c r="C90">
+        <v>539.37</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91">
-        <v>507.95</v>
+        <v>3</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1136.27</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C92">
-        <v>429.65</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B93" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C93">
-        <v>720.79</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94">
-        <v>451.19</v>
+        <v>3</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>479.73</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B96" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C96">
-        <v>705.94</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B97" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>524.41999999999996</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C98">
-        <v>509.26</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B99" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C99">
-        <v>663.05</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>439.45</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101">
-        <v>446.07</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B102" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C102">
-        <v>692.07</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>447.4</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="B104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104">
-        <v>403.4</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B105" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105">
-        <v>669.52</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>466.82</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C107">
-        <v>486.91</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B108" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C108">
-        <v>659.67</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C109">
-        <v>471.71</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110">
-        <v>532.58000000000004</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B111" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C111">
-        <v>703.37</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>562.97</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C113">
-        <v>505.15</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B114" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C114">
-        <v>668.52</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>506.5</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C116">
-        <v>571.26</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B117" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C117">
-        <v>570.80999999999995</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>582.09</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>449.56</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B120" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C120">
-        <v>420.48</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>454.06</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B122" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122">
-        <v>505.54</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B123" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C123">
-        <v>493.46</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>487.21</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="B125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C125">
-        <v>579.72</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B126" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C126">
-        <v>570.92999999999995</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>591.13</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B128" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C128">
-        <v>531.26</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B129" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C129">
-        <v>547.42999999999995</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>537.16999999999996</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B131" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C131">
-        <v>512.42999999999995</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B132" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C132">
-        <v>516.32000000000005</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>506.59</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C134">
-        <v>480.14</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B135" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C135">
-        <v>477.63</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>451.42</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>440.24</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B138" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C138">
-        <v>473.37</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>471.83</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="B140" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C140">
-        <v>413.27</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B141" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C141">
-        <v>457.2</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>399.36</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>576.4</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B144" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C144">
-        <v>458.96</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>429.68</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B146" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C146">
-        <v>469.28</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B147" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C147">
-        <v>462.4</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C148">
-        <v>446.33</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B149" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C149">
-        <v>514.92999999999995</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C150">
-        <v>524.33000000000004</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>492.66</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C152">
-        <v>525.04</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C153">
-        <v>555.08000000000004</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>516.41999999999996</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C155">
-        <v>529.30999999999995</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B156" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C156">
-        <v>544.63</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>646.28</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C158">
-        <v>467.75</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C159">
-        <v>496.42</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C160">
-        <v>566.66</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C161">
-        <v>435.83</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B162" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C162">
-        <v>468.24</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C163">
-        <v>507.5</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="B164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C164">
-        <v>513.24</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B165" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C165">
-        <v>442.08</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C166">
-        <v>490.51</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C167">
-        <v>455.23</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B168" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C168">
-        <v>390.46</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C169">
-        <v>490.96</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C170">
-        <v>416.64</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B171" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C171">
-        <v>473.63</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C172">
-        <v>517.11</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173">
-        <v>481.26</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B174" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C174">
-        <v>633.22</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C175">
-        <v>557.57000000000005</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B176" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C176">
-        <v>595.71</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B177" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C177">
-        <v>600.36</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C178">
-        <v>508.81</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C179">
-        <v>598.64</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B180" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C180">
-        <v>490.83</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C181">
-        <v>427.5</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C182">
-        <v>270.85000000000002</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B183" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="2">
-        <v>333.98</v>
+        <v>7</v>
+      </c>
+      <c r="C183">
+        <v>598.64</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C184">
-        <v>184.94</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C185">
-        <v>296.23</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B186" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="2">
-        <v>270.06</v>
+        <v>7</v>
+      </c>
+      <c r="C186">
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
-      </c>
-      <c r="C187">
-        <v>284.88</v>
+        <v>3</v>
+      </c>
+      <c r="C187" s="2">
+        <v>333.98</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C188">
-        <v>336.5</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B189" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="2">
-        <v>606.85</v>
+        <v>7</v>
+      </c>
+      <c r="C189">
+        <v>296.23</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
-      </c>
-      <c r="C190">
-        <v>713.78</v>
+        <v>3</v>
+      </c>
+      <c r="C190" s="2">
+        <v>270.06</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C191">
-        <v>766.34</v>
+        <v>284.88</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B192" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="2">
-        <v>536.29</v>
+        <v>7</v>
+      </c>
+      <c r="C192">
+        <v>336.5</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B193" t="s">
-        <v>6</v>
-      </c>
-      <c r="C193">
-        <v>509.61</v>
+        <v>3</v>
+      </c>
+      <c r="C193" s="2">
+        <v>606.85</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B194" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C194">
-        <v>750.08</v>
+        <v>713.78</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B195" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195">
+        <v>766.34</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B196" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="2">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B197" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B198" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="1">
         <v>46132</v>
       </c>
-      <c r="B195" t="s">
-        <v>7</v>
-      </c>
-      <c r="C195" s="2">
+      <c r="B199" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="2">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" s="1"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" s="1"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" s="1"/>
-      <c r="C198" s="2"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" s="1"/>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="1"/>
@@ -5466,6 +5547,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
+      <c r="C202" s="2"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="1"/>
@@ -5476,8 +5558,20 @@
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="1"/>
     </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="1"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="1"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="1"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C171" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
+  <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701B9EF7-BDA3-4B29-9B5B-8DF30388537C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B53C4A-30C4-4FFA-B94F-80CB6D0AA621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="16">
   <si>
     <t>Day</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>Nasik-Search-Buy-UsedCar-8april</t>
-  </si>
-  <si>
-    <t>UCR-Lead-Luxury-Cart-Classified-Jan25</t>
   </si>
 </sst>
 </file>
@@ -468,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C260"/>
+  <dimension ref="A1:C272"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3333,6 +3330,138 @@
       </c>
       <c r="C260">
         <v>1122.45</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261">
+        <v>737.82</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B262" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262">
+        <v>829.17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B263" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263">
+        <v>736.29</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B264" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264">
+        <v>1335.32</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B265" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265">
+        <v>1315.82</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B266" t="s">
+        <v>15</v>
+      </c>
+      <c r="C266">
+        <v>1259.5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B267" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267">
+        <v>1622.87</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B268" t="s">
+        <v>4</v>
+      </c>
+      <c r="C268">
+        <v>1696.19</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269">
+        <v>1749.15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B270" t="s">
+        <v>5</v>
+      </c>
+      <c r="C270">
+        <v>1380.54</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B271" t="s">
+        <v>5</v>
+      </c>
+      <c r="C271">
+        <v>1362.67</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B272" t="s">
+        <v>5</v>
+      </c>
+      <c r="C272">
+        <v>1268.51</v>
       </c>
     </row>
   </sheetData>
@@ -3363,2206 +3492,2269 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2">
-        <v>401.76</v>
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1242.3499999999999</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>955.81</v>
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1955.28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1846.72</v>
+        <v>408.42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>759.99</v>
+        <v>7</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1135.23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>46197</v>
+        <v>46200</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>692.77</v>
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1219.55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>46197</v>
+        <v>46200</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2">
-        <v>3665.23</v>
+        <v>735.13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>683.88</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1161.17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>571.57000000000005</v>
+        <v>3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1024.46</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2">
-        <v>3915.06</v>
+        <v>1446.51</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>573</v>
+        <v>958.69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>536.23</v>
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1848.93</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2">
-        <v>3945.97</v>
+        <v>762.06</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>550.80999999999995</v>
+        <v>694.2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>544.71</v>
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3673.46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2">
-        <v>3552.22</v>
+        <v>686.03</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>540.75</v>
+        <v>571.57000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>512.22</v>
+        <v>3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3915.06</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2">
-        <v>2204</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>481.71</v>
+        <v>536.23</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>484.39</v>
+        <v>3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3945.97</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2">
-        <v>3180.49</v>
+        <v>550.80999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>486.4</v>
+        <v>544.71</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24">
-        <v>527.33000000000004</v>
+        <v>3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3552.22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2">
-        <v>3641.07</v>
+        <v>540.75</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>578.59</v>
+        <v>512.22</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27">
-        <v>481.55</v>
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2204</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2">
-        <v>3441.39</v>
+        <v>481.71</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>528.88</v>
+        <v>484.39</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30">
-        <v>459.4</v>
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3180.49</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2">
-        <v>3221.28</v>
+        <v>486.4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>478.65</v>
+        <v>527.33000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33">
-        <v>497.39</v>
+        <v>3</v>
+      </c>
+      <c r="C33" s="2">
+        <v>3641.07</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2">
-        <v>3276.72</v>
+        <v>578.59</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>451.55</v>
+        <v>481.55</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36">
-        <v>536.59</v>
+        <v>3</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3441.39</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2">
-        <v>3486.04</v>
+        <v>528.88</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>493.55</v>
+        <v>459.4</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>46186</v>
+        <v>46189</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39">
-        <v>490.37</v>
+        <v>3</v>
+      </c>
+      <c r="C39" s="2">
+        <v>3221.28</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>46186</v>
+        <v>46189</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2">
-        <v>2452.7199999999998</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>547.78</v>
+        <v>497.39</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42">
-        <v>456.13</v>
+        <v>3</v>
+      </c>
+      <c r="C42" s="2">
+        <v>3276.72</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B43" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2">
-        <v>3072.14</v>
+        <v>451.55</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>461.99</v>
+        <v>536.59</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45">
-        <v>506.52</v>
+        <v>3</v>
+      </c>
+      <c r="C45" s="2">
+        <v>3486.04</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="B46" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2">
-        <v>3183.11</v>
+        <v>493.55</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>506.99</v>
+        <v>490.37</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>46183</v>
+        <v>46186</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48">
-        <v>493.44</v>
+        <v>3</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2452.7199999999998</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46183</v>
+        <v>46186</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2">
-        <v>2587.6</v>
+        <v>547.78</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50">
-        <v>458.08</v>
+        <v>456.13</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51">
-        <v>506.82</v>
+        <v>3</v>
+      </c>
+      <c r="C51" s="2">
+        <v>3072.14</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B52" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2">
-        <v>3838.27</v>
+        <v>461.99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53">
-        <v>478.44</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54">
-        <v>492.98</v>
+        <v>3</v>
+      </c>
+      <c r="C54" s="2">
+        <v>3183.11</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B55" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2">
-        <v>2990.38</v>
+        <v>506.99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>512.85</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57">
-        <v>551.54</v>
+        <v>3</v>
+      </c>
+      <c r="C57" s="2">
+        <v>2587.6</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B58" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2">
-        <v>1448.25</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>46180</v>
+        <v>46182</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>533.17999999999995</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60">
-        <v>496.91</v>
+        <v>3</v>
+      </c>
+      <c r="C60" s="2">
+        <v>3838.27</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="B61" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C61" s="2">
-        <v>1318.78</v>
+        <v>478.44</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62">
-        <v>492.79</v>
+        <v>492.98</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63">
-        <v>493.28</v>
+        <v>3</v>
+      </c>
+      <c r="C63" s="2">
+        <v>2990.38</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B64" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C64" s="2">
-        <v>1276.5</v>
+        <v>512.85</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65">
-        <v>467.42</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B66" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66">
-        <v>505.85</v>
+        <v>3</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1448.25</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B67" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2">
-        <v>1257.7</v>
+        <v>533.17999999999995</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68">
-        <v>509.16</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69">
-        <v>468.33</v>
+        <v>3</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1318.78</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B70" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2">
-        <v>1267.75</v>
+        <v>492.79</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71">
-        <v>462.92</v>
+        <v>493.28</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72">
-        <v>500.73</v>
+        <v>3</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1276.5</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B73" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2">
-        <v>1284.17</v>
+        <v>467.42</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>521.47</v>
+        <v>505.85</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75">
-        <v>504.72</v>
+        <v>3</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1257.7</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B76" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2">
-        <v>1359.4</v>
+        <v>509.16</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B77" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77">
-        <v>516.37</v>
+        <v>468.33</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B78" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78">
-        <v>529.03</v>
+        <v>3</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1267.75</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B79" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2">
-        <v>1335.7</v>
+        <v>462.92</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80">
-        <v>528.64</v>
+        <v>500.73</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81">
-        <v>502.21</v>
+        <v>3</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1284.17</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B82" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2">
-        <v>1322.84</v>
+        <v>521.47</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83">
-        <v>509.86</v>
+        <v>504.72</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B84" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84">
-        <v>508.81</v>
+        <v>3</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1359.4</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B85" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2">
-        <v>1254.29</v>
+        <v>516.37</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86">
-        <v>500.59</v>
+        <v>529.03</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B87" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87">
-        <v>514.72</v>
+        <v>3</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1335.7</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B88" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2">
-        <v>1248.17</v>
+        <v>528.64</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89">
-        <v>499.91</v>
+        <v>502.21</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90">
-        <v>539.37</v>
+        <v>3</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1322.84</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B91" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2">
-        <v>1136.27</v>
+        <v>509.86</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92">
-        <v>505.09</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B93" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93">
-        <v>523.91999999999996</v>
+        <v>3</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1254.29</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B94" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C94" s="2">
-        <v>1173.17</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95">
-        <v>507.95</v>
+        <v>514.72</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96">
-        <v>429.65</v>
+        <v>3</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1248.17</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B97" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C97">
-        <v>720.79</v>
+        <v>499.91</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98">
-        <v>451.19</v>
+        <v>539.37</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99">
-        <v>479.73</v>
+        <v>3</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1136.27</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B100" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C100">
-        <v>705.94</v>
+        <v>505.09</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C101">
-        <v>524.41999999999996</v>
+        <v>523.91999999999996</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B102" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102">
-        <v>509.26</v>
+        <v>3</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1173.17</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B103" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>663.05</v>
+        <v>507.95</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C104">
-        <v>439.45</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B105" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>446.07</v>
+        <v>720.79</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B106" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C106">
-        <v>692.07</v>
+        <v>451.19</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107">
-        <v>447.4</v>
+        <v>479.73</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B108" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C108">
-        <v>403.4</v>
+        <v>705.94</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B109" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C109">
-        <v>669.52</v>
+        <v>524.41999999999996</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110">
-        <v>466.82</v>
+        <v>509.26</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>486.91</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B112" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C112">
-        <v>659.67</v>
+        <v>439.45</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B113" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113">
-        <v>471.71</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B114" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>532.58000000000004</v>
+        <v>692.07</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B115" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>703.37</v>
+        <v>447.4</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116">
-        <v>562.97</v>
+        <v>403.4</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B117" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>505.15</v>
+        <v>669.52</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B118" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C118">
-        <v>668.52</v>
+        <v>466.82</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119">
-        <v>506.5</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>571.26</v>
+        <v>659.67</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B121" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C121">
-        <v>570.80999999999995</v>
+        <v>471.71</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C122">
-        <v>582.09</v>
+        <v>532.58000000000004</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B123" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>449.56</v>
+        <v>703.37</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B124" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C124">
-        <v>420.48</v>
+        <v>562.97</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125">
-        <v>454.06</v>
+        <v>505.15</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B126" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C126">
-        <v>505.54</v>
+        <v>668.52</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B127" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>493.46</v>
+        <v>506.5</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128">
-        <v>487.21</v>
+        <v>571.26</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B129" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>579.72</v>
+        <v>570.80999999999995</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B130" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C130">
-        <v>570.92999999999995</v>
+        <v>582.09</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C131">
-        <v>591.13</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B132" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>531.26</v>
+        <v>420.48</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B133" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C133">
-        <v>547.42999999999995</v>
+        <v>454.06</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C134">
-        <v>537.16999999999996</v>
+        <v>505.54</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B135" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>512.42999999999995</v>
+        <v>493.46</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B136" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C136">
-        <v>516.32000000000005</v>
+        <v>487.21</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>506.59</v>
+        <v>579.72</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B138" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>480.14</v>
+        <v>570.92999999999995</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B139" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>477.63</v>
+        <v>591.13</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>451.42</v>
+        <v>531.26</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B141" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>440.24</v>
+        <v>547.42999999999995</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B142" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>473.37</v>
+        <v>537.16999999999996</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C143">
-        <v>471.83</v>
+        <v>512.42999999999995</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B144" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>413.27</v>
+        <v>516.32000000000005</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B145" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C145">
-        <v>457.2</v>
+        <v>506.59</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C146">
-        <v>399.36</v>
+        <v>480.14</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B147" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>576.4</v>
+        <v>477.63</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B148" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C148">
-        <v>458.96</v>
+        <v>451.42</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C149">
-        <v>429.68</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C150">
-        <v>469.28</v>
+        <v>473.37</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B151" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C151">
-        <v>462.4</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C152">
-        <v>446.33</v>
+        <v>413.27</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B153" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>514.92999999999995</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B154" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C154">
-        <v>524.33000000000004</v>
+        <v>399.36</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155">
-        <v>492.66</v>
+        <v>576.4</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>525.04</v>
+        <v>458.96</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>555.08000000000004</v>
+        <v>429.68</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158">
-        <v>516.41999999999996</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B159" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>529.30999999999995</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C160">
-        <v>544.63</v>
+        <v>446.33</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C161">
-        <v>646.28</v>
+        <v>514.92999999999995</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B162" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C162">
-        <v>467.75</v>
+        <v>524.33000000000004</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C163">
-        <v>496.42</v>
+        <v>492.66</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46145</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C164">
-        <v>566.66</v>
+        <v>525.04</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C165">
-        <v>435.83</v>
+        <v>555.08000000000004</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C166">
-        <v>468.24</v>
+        <v>516.41999999999996</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C167">
-        <v>507.5</v>
+        <v>529.30999999999995</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B168" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C168">
-        <v>513.24</v>
+        <v>544.63</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B169" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C169">
-        <v>442.08</v>
+        <v>646.28</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C170">
-        <v>490.51</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="B171" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>455.23</v>
+        <v>496.42</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="B172" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C172">
-        <v>390.46</v>
+        <v>566.66</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C173">
-        <v>490.96</v>
+        <v>435.83</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C174">
-        <v>416.64</v>
+        <v>468.24</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B175" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C175">
-        <v>473.63</v>
+        <v>507.5</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C176">
-        <v>517.11</v>
+        <v>513.24</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B177" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C177">
-        <v>481.26</v>
+        <v>442.08</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B178" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C178">
-        <v>633.22</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C179">
-        <v>557.57000000000005</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C180">
-        <v>595.71</v>
+        <v>390.46</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B181" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C181">
-        <v>600.36</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C182">
-        <v>508.81</v>
+        <v>416.64</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="B183" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C183">
-        <v>598.64</v>
+        <v>473.63</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="B184" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C184">
-        <v>490.83</v>
+        <v>517.11</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C185">
-        <v>427.5</v>
+        <v>481.26</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="B186" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C186">
-        <v>270.85000000000002</v>
+        <v>633.22</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="B187" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C187" s="2">
-        <v>333.98</v>
+        <v>557.57000000000005</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C188">
-        <v>184.94</v>
+        <v>595.71</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B189" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C189">
-        <v>296.23</v>
+        <v>600.36</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B190" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C190" s="2">
-        <v>270.06</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C191">
-        <v>284.88</v>
+        <v>598.64</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C192">
-        <v>336.5</v>
+        <v>490.83</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="B193" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C193" s="2">
-        <v>606.85</v>
+        <v>427.5</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B194" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C194">
-        <v>713.78</v>
+        <v>270.85000000000002</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C195">
-        <v>766.34</v>
+        <v>333.98</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B196" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C196" s="2">
-        <v>536.29</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B197" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C197">
-        <v>509.61</v>
+        <v>296.23</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B198" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C198">
-        <v>750.08</v>
+        <v>270.06</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B199" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" s="2">
+        <v>284.88</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B200" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200">
+        <v>336.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B201" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201">
+        <v>606.85</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B202" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" s="2">
+        <v>713.78</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B203" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203">
+        <v>766.34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B204" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204">
+        <v>536.29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B205" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205">
+        <v>509.61</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B206" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206">
+        <v>750.08</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="1">
         <v>46132</v>
       </c>
-      <c r="B199" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="2">
+      <c r="B207" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207">
         <v>313.98</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" s="1"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" s="1"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" s="1"/>
-      <c r="C202" s="2"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" s="1"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" s="1"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" s="1"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="1"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="1"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="1"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B53C4A-30C4-4FFA-B94F-80CB6D0AA621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEB5E1-75D4-4EC7-A147-B4AF1250310C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="16">
   <si>
     <t>Day</t>
   </si>
@@ -465,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C272"/>
+  <dimension ref="A1:C280"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3464,6 +3464,94 @@
         <v>1268.51</v>
       </c>
     </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B273" t="s">
+        <v>15</v>
+      </c>
+      <c r="C273">
+        <v>984.48</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B274" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274">
+        <v>1195.8699999999999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B275" t="s">
+        <v>4</v>
+      </c>
+      <c r="C275">
+        <v>1516.05</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B276" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276">
+        <v>660.86</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B277" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277">
+        <v>595.87</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B278" t="s">
+        <v>15</v>
+      </c>
+      <c r="C278">
+        <v>948.7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B279" t="s">
+        <v>4</v>
+      </c>
+      <c r="C279">
+        <v>1514.9</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B280" t="s">
+        <v>5</v>
+      </c>
+      <c r="C280">
+        <v>1144.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3471,7 +3559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C213"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -5757,10 +5845,70 @@
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="1"/>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A209" s="1"/>
+      <c r="A208" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B208" t="s">
+        <v>7</v>
+      </c>
+      <c r="C208" s="2">
+        <v>1197.1500000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B209" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="2">
+        <v>1173.45</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" s="2">
+        <v>1499.23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B211" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211" s="2">
+        <v>1228.1099999999999</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B212" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="2">
+        <v>1080.54</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B213" t="s">
+        <v>6</v>
+      </c>
+      <c r="C213">
+        <v>959</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEB5E1-75D4-4EC7-A147-B4AF1250310C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23534563-8E93-41FE-9307-82D1B020E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="19">
   <si>
     <t>Day</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>Nasik-Search-Buy-UsedCar-8april</t>
+  </si>
+  <si>
+    <t>Ahmedabad-UCD-8april-Leadform</t>
+  </si>
+  <si>
+    <t>Nashik-UCD-8april-Lead-Form</t>
+  </si>
+  <si>
+    <t>Chandigarh-UCD-8april-Leadform</t>
   </si>
 </sst>
 </file>
@@ -3559,7 +3568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -5910,6 +5919,72 @@
         <v>959</v>
       </c>
     </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B214" t="s">
+        <v>16</v>
+      </c>
+      <c r="C214">
+        <v>992.78</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B215" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" s="2">
+        <v>1839.85</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B216" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216" s="2">
+        <v>1286.07</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B217" t="s">
+        <v>7</v>
+      </c>
+      <c r="C217" s="2">
+        <v>1626.17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B218" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="2">
+        <v>1579.87</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B219" t="s">
+        <v>6</v>
+      </c>
+      <c r="C219" s="2">
+        <v>2474.1999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23534563-8E93-41FE-9307-82D1B020E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1E511-B321-4C2A-B8B8-CEE5DD2CA8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="21">
   <si>
     <t>Day</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Chandigarh-UCD-8april-Leadform</t>
+  </si>
+  <si>
+    <t>Demand-Gen-CHD-1july-UC</t>
+  </si>
+  <si>
+    <t>Demand-Gen-Nashik-1july-UC</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C280"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3559,6 +3565,72 @@
       </c>
       <c r="C280">
         <v>1144.21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B281" t="s">
+        <v>19</v>
+      </c>
+      <c r="C281">
+        <v>134.41</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B282" t="s">
+        <v>20</v>
+      </c>
+      <c r="C282">
+        <v>445.52</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B283" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283">
+        <v>726.89</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B284" t="s">
+        <v>15</v>
+      </c>
+      <c r="C284">
+        <v>1427.13</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B285" t="s">
+        <v>4</v>
+      </c>
+      <c r="C285">
+        <v>1983.57</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B286" t="s">
+        <v>5</v>
+      </c>
+      <c r="C286">
+        <v>1935.91</v>
       </c>
     </row>
   </sheetData>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1E511-B321-4C2A-B8B8-CEE5DD2CA8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700304B4-6627-45CD-BDA8-ED5B951E6840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="21">
   <si>
     <t>Day</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3633,6 +3633,72 @@
         <v>1935.91</v>
       </c>
     </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B287" t="s">
+        <v>19</v>
+      </c>
+      <c r="C287">
+        <v>1201.97</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B288" t="s">
+        <v>20</v>
+      </c>
+      <c r="C288">
+        <v>579.36</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B289" t="s">
+        <v>11</v>
+      </c>
+      <c r="C289">
+        <v>397.02</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B290" t="s">
+        <v>15</v>
+      </c>
+      <c r="C290">
+        <v>1941.37</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B291" t="s">
+        <v>4</v>
+      </c>
+      <c r="C291">
+        <v>1887.52</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B292" t="s">
+        <v>5</v>
+      </c>
+      <c r="C292">
+        <v>1948.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3640,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6057,6 +6123,72 @@
         <v>2474.1999999999998</v>
       </c>
     </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B220" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220">
+        <v>893.58</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B221" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221" s="2">
+        <v>2196.96</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B222" t="s">
+        <v>18</v>
+      </c>
+      <c r="C222" s="2">
+        <v>1472.01</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B223" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" s="2">
+        <v>1999.82</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B224" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="2">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B225" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" s="2">
+        <v>2199.21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700304B4-6627-45CD-BDA8-ED5B951E6840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D205CE-2C97-4D13-A9CF-1606F065AE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="21">
   <si>
     <t>Day</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3699,6 +3699,72 @@
         <v>1948.29</v>
       </c>
     </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B293" t="s">
+        <v>19</v>
+      </c>
+      <c r="C293">
+        <v>34.69</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B294" t="s">
+        <v>20</v>
+      </c>
+      <c r="C294">
+        <v>188.13</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B295" t="s">
+        <v>11</v>
+      </c>
+      <c r="C295">
+        <v>109.91</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B296" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296">
+        <v>1128.29</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B297" t="s">
+        <v>4</v>
+      </c>
+      <c r="C297">
+        <v>1196.19</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B298" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298">
+        <v>1202.3900000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3706,7 +3772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6189,6 +6255,72 @@
         <v>2199.21</v>
       </c>
     </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>46206</v>
+      </c>
+      <c r="B226" t="s">
+        <v>16</v>
+      </c>
+      <c r="C226">
+        <v>64.39</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>46206</v>
+      </c>
+      <c r="B227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227">
+        <v>1985.03</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>46206</v>
+      </c>
+      <c r="B228" t="s">
+        <v>18</v>
+      </c>
+      <c r="C228">
+        <v>1271.74</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>46206</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229">
+        <v>1883.71</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>46206</v>
+      </c>
+      <c r="B230" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230">
+        <v>2007.26</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>46206</v>
+      </c>
+      <c r="B231" t="s">
+        <v>6</v>
+      </c>
+      <c r="C231">
+        <v>2847.42</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D205CE-2C97-4D13-A9CF-1606F065AE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C0330-976E-4DD0-A52E-052C9D7C880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="21">
   <si>
     <t>Day</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C298"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3765,6 +3765,39 @@
         <v>1202.3900000000001</v>
       </c>
     </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B299" t="s">
+        <v>15</v>
+      </c>
+      <c r="C299">
+        <v>1240.3699999999999</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B300" t="s">
+        <v>4</v>
+      </c>
+      <c r="C300">
+        <v>1516.04</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B301" t="s">
+        <v>5</v>
+      </c>
+      <c r="C301">
+        <v>1280.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3772,7 +3805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C236"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6256,7 +6289,7 @@
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A226">
+      <c r="A226" s="1">
         <v>46206</v>
       </c>
       <c r="B226" t="s">
@@ -6267,7 +6300,7 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227">
+      <c r="A227" s="1">
         <v>46206</v>
       </c>
       <c r="B227" t="s">
@@ -6278,7 +6311,7 @@
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228">
+      <c r="A228" s="1">
         <v>46206</v>
       </c>
       <c r="B228" t="s">
@@ -6289,7 +6322,7 @@
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229">
+      <c r="A229" s="1">
         <v>46206</v>
       </c>
       <c r="B229" t="s">
@@ -6300,7 +6333,7 @@
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230">
+      <c r="A230" s="1">
         <v>46206</v>
       </c>
       <c r="B230" t="s">
@@ -6311,7 +6344,7 @@
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231">
+      <c r="A231" s="1">
         <v>46206</v>
       </c>
       <c r="B231" t="s">
@@ -6319,6 +6352,61 @@
       </c>
       <c r="C231">
         <v>2847.42</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B232" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232" s="2">
+        <v>1644.06</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B233" t="s">
+        <v>18</v>
+      </c>
+      <c r="C233" s="2">
+        <v>1871.7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" s="2">
+        <v>1918.24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B235" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="2">
+        <v>1913.24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B236" t="s">
+        <v>6</v>
+      </c>
+      <c r="C236">
+        <v>952.23</v>
       </c>
     </row>
   </sheetData>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C0330-976E-4DD0-A52E-052C9D7C880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60251346-4D08-4657-ACA0-0F5E3030A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="21">
   <si>
     <t>Day</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C304"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3798,6 +3798,39 @@
         <v>1280.07</v>
       </c>
     </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B302" t="s">
+        <v>15</v>
+      </c>
+      <c r="C302">
+        <v>1217.32</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B303" t="s">
+        <v>4</v>
+      </c>
+      <c r="C303">
+        <v>1636.02</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B304" t="s">
+        <v>5</v>
+      </c>
+      <c r="C304">
+        <v>1259.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3805,7 +3838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6409,6 +6442,61 @@
         <v>952.23</v>
       </c>
     </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" s="2">
+        <v>2272.38</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B238" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238" s="2">
+        <v>2034.9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B239" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" s="2">
+        <v>2092.1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B240" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="2">
+        <v>2640.46</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B241" t="s">
+        <v>6</v>
+      </c>
+      <c r="C241">
+        <v>203.7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60251346-4D08-4657-ACA0-0F5E3030A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A9B562-BF27-42BA-A8E1-251898C11018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="22">
   <si>
     <t>Day</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Demand-Gen-Nashik-1july-UC</t>
+  </si>
+  <si>
+    <t>Nashik-UCR-Static-Website</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C304"/>
+  <dimension ref="A1:C307"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -3831,6 +3834,39 @@
         <v>1259.97</v>
       </c>
     </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B305" t="s">
+        <v>15</v>
+      </c>
+      <c r="C305">
+        <v>1104.8399999999999</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306">
+        <v>1514.79</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B307" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307">
+        <v>1042.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3838,7 +3874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6497,6 +6533,72 @@
         <v>203.7</v>
       </c>
     </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" s="2">
+        <v>2012.96</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B243" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" s="2">
+        <v>1931.96</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="2">
+        <v>2196.63</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B245" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="2">
+        <v>2910.37</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B246" t="s">
+        <v>6</v>
+      </c>
+      <c r="C246">
+        <v>832.99</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B247" t="s">
+        <v>21</v>
+      </c>
+      <c r="C247">
+        <v>626.26</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C175" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
